--- a/public/templates/cp12.xlsx
+++ b/public/templates/cp12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat2025\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB5C7E2-3D49-4178-9959-73DBC5CAEECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8A168F-57AC-4A7E-B23C-915BB541FD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="40">
   <si>
     <t>Nº</t>
   </si>
@@ -144,16 +144,13 @@
     <t>2 de 2</t>
   </si>
   <si>
-    <t>Lenguaje [45%]</t>
-  </si>
-  <si>
-    <t>Quechua [5%]</t>
-  </si>
-  <si>
     <t>Inglés [50%]</t>
   </si>
   <si>
     <t>Leng. e Inglés [100%]</t>
+  </si>
+  <si>
+    <t>Lenguaje [50%]</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1117,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1422,6 +1419,18 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1434,6 +1443,39 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1448,57 +1490,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="23" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="72">
@@ -2053,41 +2044,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CF58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:CB58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
-    <col min="3" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" style="2" customWidth="1"/>
-    <col min="14" max="16" width="4.7109375" customWidth="1"/>
-    <col min="17" max="17" width="4.7109375" style="2" customWidth="1"/>
-    <col min="18" max="20" width="4.7109375" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" style="2" customWidth="1"/>
-    <col min="22" max="24" width="4.7109375" customWidth="1"/>
-    <col min="25" max="25" width="4.7109375" style="2" customWidth="1"/>
-    <col min="26" max="28" width="4.7109375" customWidth="1"/>
-    <col min="29" max="29" width="4.7109375" style="2" customWidth="1"/>
-    <col min="30" max="32" width="4.7109375" customWidth="1"/>
-    <col min="33" max="33" width="4.7109375" style="2" customWidth="1"/>
-    <col min="34" max="36" width="4.7109375" customWidth="1"/>
-    <col min="37" max="37" width="4.7109375" style="2" customWidth="1"/>
-    <col min="38" max="40" width="4.7109375" customWidth="1"/>
-    <col min="41" max="41" width="4.7109375" style="2" customWidth="1"/>
-    <col min="42" max="42" width="4.7109375" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" customWidth="1"/>
-    <col min="44" max="44" width="38.7109375" customWidth="1"/>
-    <col min="45" max="48" width="4.7109375" customWidth="1"/>
-    <col min="49" max="52" width="4.7109375" style="2" customWidth="1"/>
-    <col min="53" max="80" width="4.7109375" customWidth="1"/>
-    <col min="81" max="82" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" customWidth="1"/>
+    <col min="2" max="2" width="39.6640625" customWidth="1"/>
+    <col min="3" max="4" width="4.6640625" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" style="2" customWidth="1"/>
+    <col min="6" max="8" width="4.6640625" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="2" customWidth="1"/>
+    <col min="10" max="12" width="4.6640625" customWidth="1"/>
+    <col min="13" max="13" width="4.6640625" style="2" customWidth="1"/>
+    <col min="14" max="16" width="4.6640625" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" style="2" customWidth="1"/>
+    <col min="18" max="20" width="4.6640625" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" style="2" customWidth="1"/>
+    <col min="22" max="24" width="4.6640625" customWidth="1"/>
+    <col min="25" max="25" width="4.6640625" style="2" customWidth="1"/>
+    <col min="26" max="28" width="4.6640625" customWidth="1"/>
+    <col min="29" max="29" width="4.6640625" style="2" customWidth="1"/>
+    <col min="30" max="32" width="4.6640625" customWidth="1"/>
+    <col min="33" max="33" width="4.6640625" style="2" customWidth="1"/>
+    <col min="34" max="36" width="4.6640625" customWidth="1"/>
+    <col min="37" max="37" width="4.6640625" style="2" customWidth="1"/>
+    <col min="38" max="40" width="4.6640625" customWidth="1"/>
+    <col min="41" max="41" width="4.6640625" style="2" customWidth="1"/>
+    <col min="42" max="42" width="4.6640625" customWidth="1"/>
+    <col min="43" max="43" width="3.88671875" customWidth="1"/>
+    <col min="44" max="44" width="38.6640625" customWidth="1"/>
+    <col min="45" max="76" width="4.6640625" customWidth="1"/>
+    <col min="77" max="78" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A2" s="99" t="s">
         <v>35</v>
       </c>
@@ -2169,12 +2158,8 @@
       <c r="BV2" s="99"/>
       <c r="BW2" s="99"/>
       <c r="BX2" s="99"/>
-      <c r="BY2" s="99"/>
-      <c r="BZ2" s="99"/>
-      <c r="CA2" s="99"/>
-      <c r="CB2" s="99"/>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A3" s="100" t="s">
         <v>13</v>
       </c>
@@ -2256,12 +2241,8 @@
       <c r="BV3" s="100"/>
       <c r="BW3" s="100"/>
       <c r="BX3" s="100"/>
-      <c r="BY3" s="100"/>
-      <c r="BZ3" s="100"/>
-      <c r="CA3" s="100"/>
-      <c r="CB3" s="100"/>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A4" s="101"/>
       <c r="B4" s="101"/>
       <c r="C4" s="101"/>
@@ -2341,12 +2322,8 @@
       <c r="BV4" s="101"/>
       <c r="BW4" s="101"/>
       <c r="BX4" s="101"/>
-      <c r="BY4" s="101"/>
-      <c r="BZ4" s="101"/>
-      <c r="CA4" s="101"/>
-      <c r="CB4" s="101"/>
     </row>
-    <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:76" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="102"/>
       <c r="B5" s="102"/>
       <c r="C5" s="102"/>
@@ -2426,142 +2403,132 @@
       <c r="BV5" s="102"/>
       <c r="BW5" s="102"/>
       <c r="BX5" s="102"/>
-      <c r="BY5" s="102"/>
-      <c r="BZ5" s="102"/>
-      <c r="CA5" s="102"/>
-      <c r="CB5" s="102"/>
     </row>
-    <row r="6" spans="1:80" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="112" t="s">
+    <row r="6" spans="1:76" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="C6" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="104"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="103" t="s">
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="104"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="107" t="s">
+      <c r="H6" s="108"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="104"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="103" t="s">
+      <c r="L6" s="108"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="104"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="106"/>
-      <c r="S6" s="103" t="s">
+      <c r="P6" s="108"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="T6" s="104"/>
-      <c r="U6" s="105"/>
-      <c r="V6" s="106"/>
-      <c r="W6" s="107" t="s">
+      <c r="T6" s="108"/>
+      <c r="U6" s="109"/>
+      <c r="V6" s="110"/>
+      <c r="W6" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="X6" s="104"/>
-      <c r="Y6" s="105"/>
-      <c r="Z6" s="105"/>
-      <c r="AA6" s="103" t="s">
+      <c r="X6" s="108"/>
+      <c r="Y6" s="109"/>
+      <c r="Z6" s="109"/>
+      <c r="AA6" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="AB6" s="104"/>
-      <c r="AC6" s="105"/>
-      <c r="AD6" s="106"/>
-      <c r="AE6" s="103" t="s">
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="109"/>
+      <c r="AD6" s="110"/>
+      <c r="AE6" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="AF6" s="104"/>
-      <c r="AG6" s="105"/>
-      <c r="AH6" s="106"/>
-      <c r="AI6" s="107" t="s">
+      <c r="AF6" s="108"/>
+      <c r="AG6" s="109"/>
+      <c r="AH6" s="110"/>
+      <c r="AI6" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="AJ6" s="104"/>
-      <c r="AK6" s="105"/>
-      <c r="AL6" s="105"/>
-      <c r="AM6" s="108" t="s">
+      <c r="AJ6" s="108"/>
+      <c r="AK6" s="109"/>
+      <c r="AL6" s="109"/>
+      <c r="AM6" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="AN6" s="109"/>
-      <c r="AO6" s="110"/>
-      <c r="AP6" s="111"/>
-      <c r="AQ6" s="112" t="s">
+      <c r="AN6" s="124"/>
+      <c r="AO6" s="125"/>
+      <c r="AP6" s="126"/>
+      <c r="AQ6" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="AR6" s="121" t="s">
+      <c r="AR6" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="AS6" s="117" t="s">
+      <c r="AS6" s="103" t="s">
+        <v>39</v>
+      </c>
+      <c r="AT6" s="104"/>
+      <c r="AU6" s="105"/>
+      <c r="AV6" s="106"/>
+      <c r="AW6" s="115" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX6" s="104"/>
+      <c r="AY6" s="105"/>
+      <c r="AZ6" s="105"/>
+      <c r="BA6" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="BB6" s="104"/>
+      <c r="BC6" s="105"/>
+      <c r="BD6" s="106"/>
+      <c r="BE6" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="AT6" s="118"/>
-      <c r="AU6" s="119"/>
-      <c r="AV6" s="120"/>
-      <c r="AW6" s="117" t="s">
+      <c r="BF6" s="104"/>
+      <c r="BG6" s="105"/>
+      <c r="BH6" s="106"/>
+      <c r="BI6" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="AX6" s="118"/>
-      <c r="AY6" s="119"/>
-      <c r="AZ6" s="120"/>
-      <c r="BA6" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="BB6" s="118"/>
-      <c r="BC6" s="119"/>
-      <c r="BD6" s="119"/>
-      <c r="BE6" s="117" t="s">
-        <v>15</v>
-      </c>
-      <c r="BF6" s="118"/>
-      <c r="BG6" s="119"/>
-      <c r="BH6" s="120"/>
-      <c r="BI6" s="117" t="s">
-        <v>39</v>
-      </c>
-      <c r="BJ6" s="118"/>
-      <c r="BK6" s="119"/>
-      <c r="BL6" s="120"/>
+      <c r="BJ6" s="108"/>
+      <c r="BK6" s="109"/>
+      <c r="BL6" s="110"/>
       <c r="BM6" s="103" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="BN6" s="104"/>
       <c r="BO6" s="105"/>
-      <c r="BP6" s="106"/>
-      <c r="BQ6" s="117" t="s">
-        <v>8</v>
-      </c>
-      <c r="BR6" s="118"/>
-      <c r="BS6" s="119"/>
-      <c r="BT6" s="119"/>
-      <c r="BU6" s="117" t="s">
+      <c r="BP6" s="105"/>
+      <c r="BQ6" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="BV6" s="118"/>
-      <c r="BW6" s="119"/>
-      <c r="BX6" s="120"/>
-      <c r="BY6" s="103" t="s">
+      <c r="BR6" s="104"/>
+      <c r="BS6" s="105"/>
+      <c r="BT6" s="106"/>
+      <c r="BU6" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="BZ6" s="104"/>
-      <c r="CA6" s="105"/>
-      <c r="CB6" s="106"/>
+      <c r="BV6" s="108"/>
+      <c r="BW6" s="109"/>
+      <c r="BX6" s="110"/>
     </row>
-    <row r="7" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="113"/>
-      <c r="B7" s="122"/>
+    <row r="7" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="121"/>
+      <c r="B7" s="119"/>
       <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
@@ -2682,8 +2649,8 @@
       <c r="AP7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AQ7" s="113"/>
-      <c r="AR7" s="122"/>
+      <c r="AQ7" s="121"/>
+      <c r="AR7" s="119"/>
       <c r="AS7" s="11" t="s">
         <v>26</v>
       </c>
@@ -2732,28 +2699,28 @@
       <c r="BH7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="BI7" s="11" t="s">
+      <c r="BI7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="BJ7" s="12" t="s">
+      <c r="BJ7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="BK7" s="13" t="s">
+      <c r="BK7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="BL7" s="14" t="s">
+      <c r="BL7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="BM7" s="3" t="s">
+      <c r="BM7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="BN7" s="4" t="s">
+      <c r="BN7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="BO7" s="5" t="s">
+      <c r="BO7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BP7" s="14" t="s">
         <v>29</v>
       </c>
       <c r="BQ7" s="11" t="s">
@@ -2768,42 +2735,30 @@
       <c r="BT7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="BU7" s="11" t="s">
+      <c r="BU7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="BV7" s="12" t="s">
+      <c r="BV7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="BW7" s="13" t="s">
+      <c r="BW7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="BX7" s="14" t="s">
+      <c r="BX7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="BY7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="BZ7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="CA7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="CB7" s="6" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="8" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>1</v>
       </c>
       <c r="B8" s="60"/>
       <c r="C8" s="16" t="str">
-        <f>IF(BM8="","",BM8)</f>
+        <f>IF(BI8="","",BI8)</f>
         <v/>
       </c>
       <c r="D8" s="17" t="str">
-        <f t="shared" ref="D8:F8" si="1">IF(BN8="","",BN8)</f>
+        <f t="shared" ref="D8:F8" si="1">IF(BJ8="","",BJ8)</f>
         <v/>
       </c>
       <c r="E8" s="18" t="str">
@@ -2857,11 +2812,11 @@
         <v/>
       </c>
       <c r="AE8" s="16" t="str">
-        <f>IF(BY8="","",BY8)</f>
+        <f>IF(BU8="","",BU8)</f>
         <v/>
       </c>
       <c r="AF8" s="17" t="str">
-        <f t="shared" ref="AF8:AH8" si="2">IF(BZ8="","",BZ8)</f>
+        <f t="shared" ref="AF8:AH8" si="2">IF(BV8="","",BV8)</f>
         <v/>
       </c>
       <c r="AG8" s="18" t="str">
@@ -2900,17 +2855,17 @@
         <f>IF(SUM(AS8:AU8)=0,"",ROUND(AVERAGE(AS8:AU8),0))</f>
         <v/>
       </c>
-      <c r="AW8" s="25"/>
+      <c r="AW8" s="29"/>
       <c r="AX8" s="26"/>
       <c r="AY8" s="27"/>
-      <c r="AZ8" s="28" t="str">
+      <c r="AZ8" s="27" t="str">
         <f>IF(SUM(AW8:AY8)=0,"",ROUND(AVERAGE(AW8:AY8),0))</f>
         <v/>
       </c>
-      <c r="BA8" s="29"/>
+      <c r="BA8" s="25"/>
       <c r="BB8" s="26"/>
       <c r="BC8" s="27"/>
-      <c r="BD8" s="27" t="str">
+      <c r="BD8" s="28" t="str">
         <f>IF(SUM(BA8:BC8)=0,"",ROUND(AVERAGE(BA8:BC8),0))</f>
         <v/>
       </c>
@@ -2921,61 +2876,54 @@
         <f>IF(SUM(BE8:BG8)=0,"",ROUND(AVERAGE(BE8:BG8),0))</f>
         <v/>
       </c>
-      <c r="BI8" s="25"/>
-      <c r="BJ8" s="26"/>
-      <c r="BK8" s="27"/>
-      <c r="BL8" s="28" t="str">
+      <c r="BI8" s="16"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="18"/>
+      <c r="BL8" s="19" t="str">
         <f>IF(SUM(BI8:BK8)=0,"",ROUND(AVERAGE(BI8:BK8),0))</f>
         <v/>
       </c>
-      <c r="BM8" s="16"/>
-      <c r="BN8" s="17"/>
-      <c r="BO8" s="18"/>
-      <c r="BP8" s="19" t="str">
+      <c r="BM8" s="29"/>
+      <c r="BN8" s="26"/>
+      <c r="BO8" s="27"/>
+      <c r="BP8" s="27" t="str">
         <f>IF(SUM(BM8:BO8)=0,"",ROUND(AVERAGE(BM8:BO8),0))</f>
         <v/>
       </c>
-      <c r="BQ8" s="29"/>
+      <c r="BQ8" s="25"/>
       <c r="BR8" s="26"/>
       <c r="BS8" s="27"/>
-      <c r="BT8" s="27" t="str">
+      <c r="BT8" s="28" t="str">
         <f>IF(SUM(BQ8:BS8)=0,"",ROUND(AVERAGE(BQ8:BS8),0))</f>
         <v/>
       </c>
-      <c r="BU8" s="25"/>
-      <c r="BV8" s="26"/>
-      <c r="BW8" s="27"/>
-      <c r="BX8" s="28" t="str">
+      <c r="BU8" s="16"/>
+      <c r="BV8" s="17"/>
+      <c r="BW8" s="18"/>
+      <c r="BX8" s="19" t="str">
         <f>IF(SUM(BU8:BW8)=0,"",ROUND(AVERAGE(BU8:BW8),0))</f>
         <v/>
       </c>
-      <c r="BY8" s="16"/>
-      <c r="BZ8" s="17"/>
-      <c r="CA8" s="18"/>
-      <c r="CB8" s="19" t="str">
-        <f>IF(SUM(BY8:CA8)=0,"",ROUND(AVERAGE(BY8:CA8),0))</f>
-        <v/>
-      </c>
     </row>
-    <row r="9" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30">
         <v>2</v>
       </c>
       <c r="B9" s="61"/>
       <c r="C9" s="31" t="str">
-        <f t="shared" ref="C9:C37" si="4">IF(BM9="","",BM9)</f>
+        <f t="shared" ref="C9:C37" si="4">IF(BI9="","",BI9)</f>
         <v/>
       </c>
       <c r="D9" s="32" t="str">
-        <f t="shared" ref="D9:D37" si="5">IF(BN9="","",BN9)</f>
+        <f t="shared" ref="D9:D37" si="5">IF(BJ9="","",BJ9)</f>
         <v/>
       </c>
       <c r="E9" s="33" t="str">
-        <f t="shared" ref="E9:E37" si="6">IF(BO9="","",BO9)</f>
+        <f t="shared" ref="E9:E37" si="6">IF(BK9="","",BK9)</f>
         <v/>
       </c>
       <c r="F9" s="34" t="str">
-        <f t="shared" ref="F9:F37" si="7">IF(BP9="","",BP9)</f>
+        <f t="shared" ref="F9:F37" si="7">IF(BL9="","",BL9)</f>
         <v/>
       </c>
       <c r="G9" s="31"/>
@@ -3021,19 +2969,19 @@
         <v/>
       </c>
       <c r="AE9" s="31" t="str">
-        <f t="shared" ref="AE9:AE37" si="14">IF(BY9="","",BY9)</f>
+        <f t="shared" ref="AE9:AE37" si="14">IF(BU9="","",BU9)</f>
         <v/>
       </c>
       <c r="AF9" s="32" t="str">
-        <f t="shared" ref="AF9:AF37" si="15">IF(BZ9="","",BZ9)</f>
+        <f t="shared" ref="AF9:AF37" si="15">IF(BV9="","",BV9)</f>
         <v/>
       </c>
       <c r="AG9" s="33" t="str">
-        <f t="shared" ref="AG9:AG37" si="16">IF(CA9="","",CA9)</f>
+        <f t="shared" ref="AG9:AG37" si="16">IF(BW9="","",BW9)</f>
         <v/>
       </c>
       <c r="AH9" s="34" t="str">
-        <f t="shared" ref="AH9:AH37" si="17">IF(CB9="","",CB9)</f>
+        <f t="shared" ref="AH9:AH37" si="17">IF(BX9="","",BX9)</f>
         <v/>
       </c>
       <c r="AI9" s="31"/>
@@ -3064,17 +3012,17 @@
         <f t="shared" ref="AV9:AV37" si="20">IF(SUM(AS9:AU9)=0,"",ROUND(AVERAGE(AS9:AU9),0))</f>
         <v/>
       </c>
-      <c r="AW9" s="40"/>
+      <c r="AW9" s="44"/>
       <c r="AX9" s="41"/>
       <c r="AY9" s="42"/>
-      <c r="AZ9" s="43" t="str">
+      <c r="AZ9" s="42" t="str">
         <f t="shared" ref="AZ9:AZ37" si="21">IF(SUM(AW9:AY9)=0,"",ROUND(AVERAGE(AW9:AY9),0))</f>
         <v/>
       </c>
-      <c r="BA9" s="44"/>
+      <c r="BA9" s="40"/>
       <c r="BB9" s="41"/>
       <c r="BC9" s="42"/>
-      <c r="BD9" s="42" t="str">
+      <c r="BD9" s="43" t="str">
         <f t="shared" ref="BD9:BD37" si="22">IF(SUM(BA9:BC9)=0,"",ROUND(AVERAGE(BA9:BC9),0))</f>
         <v/>
       </c>
@@ -3085,43 +3033,36 @@
         <f t="shared" ref="BH9:BH37" si="23">IF(SUM(BE9:BG9)=0,"",ROUND(AVERAGE(BE9:BG9),0))</f>
         <v/>
       </c>
-      <c r="BI9" s="40"/>
-      <c r="BJ9" s="41"/>
-      <c r="BK9" s="42"/>
-      <c r="BL9" s="43" t="str">
+      <c r="BI9" s="31"/>
+      <c r="BJ9" s="32"/>
+      <c r="BK9" s="33"/>
+      <c r="BL9" s="34" t="str">
         <f t="shared" ref="BL9:BL37" si="24">IF(SUM(BI9:BK9)=0,"",ROUND(AVERAGE(BI9:BK9),0))</f>
         <v/>
       </c>
-      <c r="BM9" s="31"/>
-      <c r="BN9" s="32"/>
-      <c r="BO9" s="33"/>
-      <c r="BP9" s="34" t="str">
+      <c r="BM9" s="44"/>
+      <c r="BN9" s="41"/>
+      <c r="BO9" s="42"/>
+      <c r="BP9" s="42" t="str">
         <f t="shared" ref="BP9:BP37" si="25">IF(SUM(BM9:BO9)=0,"",ROUND(AVERAGE(BM9:BO9),0))</f>
         <v/>
       </c>
-      <c r="BQ9" s="44"/>
+      <c r="BQ9" s="40"/>
       <c r="BR9" s="41"/>
       <c r="BS9" s="42"/>
-      <c r="BT9" s="42" t="str">
+      <c r="BT9" s="43" t="str">
         <f t="shared" ref="BT9:BT37" si="26">IF(SUM(BQ9:BS9)=0,"",ROUND(AVERAGE(BQ9:BS9),0))</f>
         <v/>
       </c>
-      <c r="BU9" s="40"/>
-      <c r="BV9" s="41"/>
-      <c r="BW9" s="42"/>
-      <c r="BX9" s="43" t="str">
+      <c r="BU9" s="31"/>
+      <c r="BV9" s="32"/>
+      <c r="BW9" s="33"/>
+      <c r="BX9" s="34" t="str">
         <f t="shared" ref="BX9:BX37" si="27">IF(SUM(BU9:BW9)=0,"",ROUND(AVERAGE(BU9:BW9),0))</f>
         <v/>
       </c>
-      <c r="BY9" s="31"/>
-      <c r="BZ9" s="32"/>
-      <c r="CA9" s="33"/>
-      <c r="CB9" s="34" t="str">
-        <f t="shared" ref="CB9:CB37" si="28">IF(SUM(BY9:CA9)=0,"",ROUND(AVERAGE(BY9:CA9),0))</f>
-        <v/>
-      </c>
     </row>
-    <row r="10" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="30">
         <v>3</v>
       </c>
@@ -3228,17 +3169,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW10" s="40"/>
+      <c r="AW10" s="44"/>
       <c r="AX10" s="41"/>
       <c r="AY10" s="42"/>
-      <c r="AZ10" s="43" t="str">
+      <c r="AZ10" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA10" s="44"/>
+      <c r="BA10" s="40"/>
       <c r="BB10" s="41"/>
       <c r="BC10" s="42"/>
-      <c r="BD10" s="42" t="str">
+      <c r="BD10" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -3249,43 +3190,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI10" s="40"/>
-      <c r="BJ10" s="41"/>
-      <c r="BK10" s="42"/>
-      <c r="BL10" s="43" t="str">
+      <c r="BI10" s="31"/>
+      <c r="BJ10" s="32"/>
+      <c r="BK10" s="33"/>
+      <c r="BL10" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM10" s="31"/>
-      <c r="BN10" s="32"/>
-      <c r="BO10" s="33"/>
-      <c r="BP10" s="34" t="str">
+      <c r="BM10" s="44"/>
+      <c r="BN10" s="41"/>
+      <c r="BO10" s="42"/>
+      <c r="BP10" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ10" s="44"/>
+      <c r="BQ10" s="40"/>
       <c r="BR10" s="41"/>
       <c r="BS10" s="42"/>
-      <c r="BT10" s="42" t="str">
+      <c r="BT10" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU10" s="40"/>
-      <c r="BV10" s="41"/>
-      <c r="BW10" s="42"/>
-      <c r="BX10" s="43" t="str">
+      <c r="BU10" s="31"/>
+      <c r="BV10" s="32"/>
+      <c r="BW10" s="33"/>
+      <c r="BX10" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY10" s="31"/>
-      <c r="BZ10" s="32"/>
-      <c r="CA10" s="33"/>
-      <c r="CB10" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="11" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="30">
         <v>4</v>
       </c>
@@ -3392,17 +3326,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW11" s="40"/>
+      <c r="AW11" s="44"/>
       <c r="AX11" s="41"/>
       <c r="AY11" s="42"/>
-      <c r="AZ11" s="43" t="str">
+      <c r="AZ11" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA11" s="44"/>
+      <c r="BA11" s="40"/>
       <c r="BB11" s="41"/>
       <c r="BC11" s="42"/>
-      <c r="BD11" s="42" t="str">
+      <c r="BD11" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -3413,43 +3347,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI11" s="40"/>
-      <c r="BJ11" s="41"/>
-      <c r="BK11" s="42"/>
-      <c r="BL11" s="43" t="str">
+      <c r="BI11" s="31"/>
+      <c r="BJ11" s="32"/>
+      <c r="BK11" s="33"/>
+      <c r="BL11" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM11" s="31"/>
-      <c r="BN11" s="32"/>
-      <c r="BO11" s="33"/>
-      <c r="BP11" s="34" t="str">
+      <c r="BM11" s="44"/>
+      <c r="BN11" s="41"/>
+      <c r="BO11" s="42"/>
+      <c r="BP11" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ11" s="44"/>
+      <c r="BQ11" s="40"/>
       <c r="BR11" s="41"/>
       <c r="BS11" s="42"/>
-      <c r="BT11" s="42" t="str">
+      <c r="BT11" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU11" s="40"/>
-      <c r="BV11" s="41"/>
-      <c r="BW11" s="42"/>
-      <c r="BX11" s="43" t="str">
+      <c r="BU11" s="31"/>
+      <c r="BV11" s="32"/>
+      <c r="BW11" s="33"/>
+      <c r="BX11" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY11" s="31"/>
-      <c r="BZ11" s="32"/>
-      <c r="CA11" s="33"/>
-      <c r="CB11" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="12" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="30">
         <v>5</v>
       </c>
@@ -3556,17 +3483,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW12" s="40"/>
+      <c r="AW12" s="44"/>
       <c r="AX12" s="41"/>
       <c r="AY12" s="42"/>
-      <c r="AZ12" s="43" t="str">
+      <c r="AZ12" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA12" s="44"/>
+      <c r="BA12" s="40"/>
       <c r="BB12" s="41"/>
       <c r="BC12" s="42"/>
-      <c r="BD12" s="42" t="str">
+      <c r="BD12" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -3577,43 +3504,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI12" s="40"/>
-      <c r="BJ12" s="41"/>
-      <c r="BK12" s="42"/>
-      <c r="BL12" s="43" t="str">
+      <c r="BI12" s="31"/>
+      <c r="BJ12" s="32"/>
+      <c r="BK12" s="33"/>
+      <c r="BL12" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM12" s="31"/>
-      <c r="BN12" s="32"/>
-      <c r="BO12" s="33"/>
-      <c r="BP12" s="34" t="str">
+      <c r="BM12" s="44"/>
+      <c r="BN12" s="41"/>
+      <c r="BO12" s="42"/>
+      <c r="BP12" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ12" s="44"/>
+      <c r="BQ12" s="40"/>
       <c r="BR12" s="41"/>
       <c r="BS12" s="42"/>
-      <c r="BT12" s="42" t="str">
+      <c r="BT12" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU12" s="40"/>
-      <c r="BV12" s="41"/>
-      <c r="BW12" s="42"/>
-      <c r="BX12" s="43" t="str">
+      <c r="BU12" s="31"/>
+      <c r="BV12" s="32"/>
+      <c r="BW12" s="33"/>
+      <c r="BX12" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY12" s="31"/>
-      <c r="BZ12" s="32"/>
-      <c r="CA12" s="33"/>
-      <c r="CB12" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="13" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="30">
         <v>6</v>
       </c>
@@ -3720,17 +3640,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW13" s="40"/>
+      <c r="AW13" s="44"/>
       <c r="AX13" s="41"/>
       <c r="AY13" s="42"/>
-      <c r="AZ13" s="43" t="str">
+      <c r="AZ13" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA13" s="44"/>
+      <c r="BA13" s="40"/>
       <c r="BB13" s="41"/>
       <c r="BC13" s="42"/>
-      <c r="BD13" s="42" t="str">
+      <c r="BD13" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -3741,43 +3661,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI13" s="40"/>
-      <c r="BJ13" s="41"/>
-      <c r="BK13" s="42"/>
-      <c r="BL13" s="43" t="str">
+      <c r="BI13" s="31"/>
+      <c r="BJ13" s="32"/>
+      <c r="BK13" s="33"/>
+      <c r="BL13" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM13" s="31"/>
-      <c r="BN13" s="32"/>
-      <c r="BO13" s="33"/>
-      <c r="BP13" s="34" t="str">
+      <c r="BM13" s="44"/>
+      <c r="BN13" s="41"/>
+      <c r="BO13" s="42"/>
+      <c r="BP13" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ13" s="44"/>
+      <c r="BQ13" s="40"/>
       <c r="BR13" s="41"/>
       <c r="BS13" s="42"/>
-      <c r="BT13" s="42" t="str">
+      <c r="BT13" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU13" s="40"/>
-      <c r="BV13" s="41"/>
-      <c r="BW13" s="42"/>
-      <c r="BX13" s="43" t="str">
+      <c r="BU13" s="31"/>
+      <c r="BV13" s="32"/>
+      <c r="BW13" s="33"/>
+      <c r="BX13" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY13" s="31"/>
-      <c r="BZ13" s="32"/>
-      <c r="CA13" s="33"/>
-      <c r="CB13" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="14" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="30">
         <v>7</v>
       </c>
@@ -3884,17 +3797,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW14" s="40"/>
+      <c r="AW14" s="44"/>
       <c r="AX14" s="41"/>
       <c r="AY14" s="42"/>
-      <c r="AZ14" s="43" t="str">
+      <c r="AZ14" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA14" s="44"/>
+      <c r="BA14" s="40"/>
       <c r="BB14" s="41"/>
       <c r="BC14" s="42"/>
-      <c r="BD14" s="42" t="str">
+      <c r="BD14" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -3905,43 +3818,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI14" s="40"/>
-      <c r="BJ14" s="41"/>
-      <c r="BK14" s="42"/>
-      <c r="BL14" s="43" t="str">
+      <c r="BI14" s="31"/>
+      <c r="BJ14" s="32"/>
+      <c r="BK14" s="33"/>
+      <c r="BL14" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM14" s="31"/>
-      <c r="BN14" s="32"/>
-      <c r="BO14" s="33"/>
-      <c r="BP14" s="34" t="str">
+      <c r="BM14" s="44"/>
+      <c r="BN14" s="41"/>
+      <c r="BO14" s="42"/>
+      <c r="BP14" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ14" s="44"/>
+      <c r="BQ14" s="40"/>
       <c r="BR14" s="41"/>
       <c r="BS14" s="42"/>
-      <c r="BT14" s="42" t="str">
+      <c r="BT14" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU14" s="40"/>
-      <c r="BV14" s="41"/>
-      <c r="BW14" s="42"/>
-      <c r="BX14" s="43" t="str">
+      <c r="BU14" s="31"/>
+      <c r="BV14" s="32"/>
+      <c r="BW14" s="33"/>
+      <c r="BX14" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY14" s="31"/>
-      <c r="BZ14" s="32"/>
-      <c r="CA14" s="33"/>
-      <c r="CB14" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="15" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="30">
         <v>8</v>
       </c>
@@ -4048,17 +3954,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW15" s="40"/>
+      <c r="AW15" s="44"/>
       <c r="AX15" s="41"/>
       <c r="AY15" s="42"/>
-      <c r="AZ15" s="43" t="str">
+      <c r="AZ15" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA15" s="44"/>
+      <c r="BA15" s="40"/>
       <c r="BB15" s="41"/>
       <c r="BC15" s="42"/>
-      <c r="BD15" s="42" t="str">
+      <c r="BD15" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -4069,43 +3975,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI15" s="40"/>
-      <c r="BJ15" s="41"/>
-      <c r="BK15" s="42"/>
-      <c r="BL15" s="43" t="str">
+      <c r="BI15" s="31"/>
+      <c r="BJ15" s="32"/>
+      <c r="BK15" s="33"/>
+      <c r="BL15" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM15" s="31"/>
-      <c r="BN15" s="32"/>
-      <c r="BO15" s="33"/>
-      <c r="BP15" s="34" t="str">
+      <c r="BM15" s="44"/>
+      <c r="BN15" s="41"/>
+      <c r="BO15" s="42"/>
+      <c r="BP15" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ15" s="44"/>
+      <c r="BQ15" s="40"/>
       <c r="BR15" s="41"/>
       <c r="BS15" s="42"/>
-      <c r="BT15" s="42" t="str">
+      <c r="BT15" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU15" s="40"/>
-      <c r="BV15" s="41"/>
-      <c r="BW15" s="42"/>
-      <c r="BX15" s="43" t="str">
+      <c r="BU15" s="31"/>
+      <c r="BV15" s="32"/>
+      <c r="BW15" s="33"/>
+      <c r="BX15" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY15" s="31"/>
-      <c r="BZ15" s="32"/>
-      <c r="CA15" s="33"/>
-      <c r="CB15" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="16" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="30">
         <v>9</v>
       </c>
@@ -4212,17 +4111,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW16" s="40"/>
+      <c r="AW16" s="44"/>
       <c r="AX16" s="41"/>
       <c r="AY16" s="42"/>
-      <c r="AZ16" s="43" t="str">
+      <c r="AZ16" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA16" s="44"/>
+      <c r="BA16" s="40"/>
       <c r="BB16" s="41"/>
       <c r="BC16" s="42"/>
-      <c r="BD16" s="42" t="str">
+      <c r="BD16" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -4233,43 +4132,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI16" s="40"/>
-      <c r="BJ16" s="41"/>
-      <c r="BK16" s="42"/>
-      <c r="BL16" s="43" t="str">
+      <c r="BI16" s="31"/>
+      <c r="BJ16" s="32"/>
+      <c r="BK16" s="33"/>
+      <c r="BL16" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM16" s="31"/>
-      <c r="BN16" s="32"/>
-      <c r="BO16" s="33"/>
-      <c r="BP16" s="34" t="str">
+      <c r="BM16" s="44"/>
+      <c r="BN16" s="41"/>
+      <c r="BO16" s="42"/>
+      <c r="BP16" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ16" s="44"/>
+      <c r="BQ16" s="40"/>
       <c r="BR16" s="41"/>
       <c r="BS16" s="42"/>
-      <c r="BT16" s="42" t="str">
+      <c r="BT16" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU16" s="40"/>
-      <c r="BV16" s="41"/>
-      <c r="BW16" s="42"/>
-      <c r="BX16" s="43" t="str">
+      <c r="BU16" s="31"/>
+      <c r="BV16" s="32"/>
+      <c r="BW16" s="33"/>
+      <c r="BX16" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY16" s="31"/>
-      <c r="BZ16" s="32"/>
-      <c r="CA16" s="33"/>
-      <c r="CB16" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="17" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30">
         <v>10</v>
       </c>
@@ -4376,17 +4268,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW17" s="40"/>
+      <c r="AW17" s="44"/>
       <c r="AX17" s="41"/>
       <c r="AY17" s="42"/>
-      <c r="AZ17" s="43" t="str">
+      <c r="AZ17" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA17" s="44"/>
+      <c r="BA17" s="40"/>
       <c r="BB17" s="41"/>
       <c r="BC17" s="42"/>
-      <c r="BD17" s="42" t="str">
+      <c r="BD17" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -4397,43 +4289,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI17" s="40"/>
-      <c r="BJ17" s="41"/>
-      <c r="BK17" s="42"/>
-      <c r="BL17" s="43" t="str">
+      <c r="BI17" s="31"/>
+      <c r="BJ17" s="32"/>
+      <c r="BK17" s="33"/>
+      <c r="BL17" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM17" s="31"/>
-      <c r="BN17" s="32"/>
-      <c r="BO17" s="33"/>
-      <c r="BP17" s="34" t="str">
+      <c r="BM17" s="44"/>
+      <c r="BN17" s="41"/>
+      <c r="BO17" s="42"/>
+      <c r="BP17" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ17" s="44"/>
+      <c r="BQ17" s="40"/>
       <c r="BR17" s="41"/>
       <c r="BS17" s="42"/>
-      <c r="BT17" s="42" t="str">
+      <c r="BT17" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU17" s="40"/>
-      <c r="BV17" s="41"/>
-      <c r="BW17" s="42"/>
-      <c r="BX17" s="43" t="str">
+      <c r="BU17" s="31"/>
+      <c r="BV17" s="32"/>
+      <c r="BW17" s="33"/>
+      <c r="BX17" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY17" s="31"/>
-      <c r="BZ17" s="32"/>
-      <c r="CA17" s="33"/>
-      <c r="CB17" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="18" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="30">
         <v>11</v>
       </c>
@@ -4540,17 +4425,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW18" s="40"/>
+      <c r="AW18" s="44"/>
       <c r="AX18" s="41"/>
       <c r="AY18" s="42"/>
-      <c r="AZ18" s="43" t="str">
+      <c r="AZ18" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA18" s="44"/>
+      <c r="BA18" s="40"/>
       <c r="BB18" s="41"/>
       <c r="BC18" s="42"/>
-      <c r="BD18" s="42" t="str">
+      <c r="BD18" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -4561,43 +4446,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI18" s="40"/>
-      <c r="BJ18" s="41"/>
-      <c r="BK18" s="42"/>
-      <c r="BL18" s="43" t="str">
+      <c r="BI18" s="31"/>
+      <c r="BJ18" s="32"/>
+      <c r="BK18" s="33"/>
+      <c r="BL18" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM18" s="31"/>
-      <c r="BN18" s="32"/>
-      <c r="BO18" s="33"/>
-      <c r="BP18" s="34" t="str">
+      <c r="BM18" s="44"/>
+      <c r="BN18" s="41"/>
+      <c r="BO18" s="42"/>
+      <c r="BP18" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ18" s="44"/>
+      <c r="BQ18" s="40"/>
       <c r="BR18" s="41"/>
       <c r="BS18" s="42"/>
-      <c r="BT18" s="42" t="str">
+      <c r="BT18" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU18" s="40"/>
-      <c r="BV18" s="41"/>
-      <c r="BW18" s="42"/>
-      <c r="BX18" s="43" t="str">
+      <c r="BU18" s="31"/>
+      <c r="BV18" s="32"/>
+      <c r="BW18" s="33"/>
+      <c r="BX18" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY18" s="31"/>
-      <c r="BZ18" s="32"/>
-      <c r="CA18" s="33"/>
-      <c r="CB18" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="19" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30">
         <v>12</v>
       </c>
@@ -4704,17 +4582,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW19" s="40"/>
+      <c r="AW19" s="44"/>
       <c r="AX19" s="41"/>
       <c r="AY19" s="42"/>
-      <c r="AZ19" s="43" t="str">
+      <c r="AZ19" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA19" s="44"/>
+      <c r="BA19" s="40"/>
       <c r="BB19" s="41"/>
       <c r="BC19" s="42"/>
-      <c r="BD19" s="42" t="str">
+      <c r="BD19" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -4725,43 +4603,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI19" s="40"/>
-      <c r="BJ19" s="41"/>
-      <c r="BK19" s="42"/>
-      <c r="BL19" s="43" t="str">
+      <c r="BI19" s="31"/>
+      <c r="BJ19" s="32"/>
+      <c r="BK19" s="33"/>
+      <c r="BL19" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM19" s="31"/>
-      <c r="BN19" s="32"/>
-      <c r="BO19" s="33"/>
-      <c r="BP19" s="34" t="str">
+      <c r="BM19" s="44"/>
+      <c r="BN19" s="41"/>
+      <c r="BO19" s="42"/>
+      <c r="BP19" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ19" s="44"/>
+      <c r="BQ19" s="40"/>
       <c r="BR19" s="41"/>
       <c r="BS19" s="42"/>
-      <c r="BT19" s="42" t="str">
+      <c r="BT19" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU19" s="40"/>
-      <c r="BV19" s="41"/>
-      <c r="BW19" s="42"/>
-      <c r="BX19" s="43" t="str">
+      <c r="BU19" s="31"/>
+      <c r="BV19" s="32"/>
+      <c r="BW19" s="33"/>
+      <c r="BX19" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY19" s="31"/>
-      <c r="BZ19" s="32"/>
-      <c r="CA19" s="33"/>
-      <c r="CB19" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="20" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="30">
         <v>13</v>
       </c>
@@ -4868,17 +4739,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW20" s="40"/>
+      <c r="AW20" s="44"/>
       <c r="AX20" s="41"/>
       <c r="AY20" s="42"/>
-      <c r="AZ20" s="43" t="str">
+      <c r="AZ20" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA20" s="44"/>
+      <c r="BA20" s="40"/>
       <c r="BB20" s="41"/>
       <c r="BC20" s="42"/>
-      <c r="BD20" s="42" t="str">
+      <c r="BD20" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -4889,43 +4760,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI20" s="40"/>
-      <c r="BJ20" s="41"/>
-      <c r="BK20" s="42"/>
-      <c r="BL20" s="43" t="str">
+      <c r="BI20" s="31"/>
+      <c r="BJ20" s="32"/>
+      <c r="BK20" s="33"/>
+      <c r="BL20" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM20" s="31"/>
-      <c r="BN20" s="32"/>
-      <c r="BO20" s="33"/>
-      <c r="BP20" s="34" t="str">
+      <c r="BM20" s="44"/>
+      <c r="BN20" s="41"/>
+      <c r="BO20" s="42"/>
+      <c r="BP20" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ20" s="44"/>
+      <c r="BQ20" s="40"/>
       <c r="BR20" s="41"/>
       <c r="BS20" s="42"/>
-      <c r="BT20" s="42" t="str">
+      <c r="BT20" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU20" s="40"/>
-      <c r="BV20" s="41"/>
-      <c r="BW20" s="42"/>
-      <c r="BX20" s="43" t="str">
+      <c r="BU20" s="31"/>
+      <c r="BV20" s="32"/>
+      <c r="BW20" s="33"/>
+      <c r="BX20" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY20" s="31"/>
-      <c r="BZ20" s="32"/>
-      <c r="CA20" s="33"/>
-      <c r="CB20" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="21" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30">
         <v>14</v>
       </c>
@@ -5032,17 +4896,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW21" s="40"/>
+      <c r="AW21" s="44"/>
       <c r="AX21" s="41"/>
       <c r="AY21" s="42"/>
-      <c r="AZ21" s="43" t="str">
+      <c r="AZ21" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA21" s="44"/>
+      <c r="BA21" s="40"/>
       <c r="BB21" s="41"/>
       <c r="BC21" s="42"/>
-      <c r="BD21" s="42" t="str">
+      <c r="BD21" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -5053,43 +4917,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI21" s="40"/>
-      <c r="BJ21" s="41"/>
-      <c r="BK21" s="42"/>
-      <c r="BL21" s="43" t="str">
+      <c r="BI21" s="31"/>
+      <c r="BJ21" s="32"/>
+      <c r="BK21" s="33"/>
+      <c r="BL21" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM21" s="31"/>
-      <c r="BN21" s="32"/>
-      <c r="BO21" s="33"/>
-      <c r="BP21" s="34" t="str">
+      <c r="BM21" s="44"/>
+      <c r="BN21" s="41"/>
+      <c r="BO21" s="42"/>
+      <c r="BP21" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ21" s="44"/>
+      <c r="BQ21" s="40"/>
       <c r="BR21" s="41"/>
       <c r="BS21" s="42"/>
-      <c r="BT21" s="42" t="str">
+      <c r="BT21" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU21" s="40"/>
-      <c r="BV21" s="41"/>
-      <c r="BW21" s="42"/>
-      <c r="BX21" s="43" t="str">
+      <c r="BU21" s="31"/>
+      <c r="BV21" s="32"/>
+      <c r="BW21" s="33"/>
+      <c r="BX21" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY21" s="31"/>
-      <c r="BZ21" s="32"/>
-      <c r="CA21" s="33"/>
-      <c r="CB21" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="22" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="30">
         <v>15</v>
       </c>
@@ -5196,17 +5053,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW22" s="40"/>
+      <c r="AW22" s="44"/>
       <c r="AX22" s="41"/>
       <c r="AY22" s="42"/>
-      <c r="AZ22" s="43" t="str">
+      <c r="AZ22" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA22" s="44"/>
+      <c r="BA22" s="40"/>
       <c r="BB22" s="41"/>
       <c r="BC22" s="42"/>
-      <c r="BD22" s="42" t="str">
+      <c r="BD22" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -5217,43 +5074,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI22" s="40"/>
-      <c r="BJ22" s="41"/>
-      <c r="BK22" s="42"/>
-      <c r="BL22" s="43" t="str">
+      <c r="BI22" s="31"/>
+      <c r="BJ22" s="32"/>
+      <c r="BK22" s="33"/>
+      <c r="BL22" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM22" s="31"/>
-      <c r="BN22" s="32"/>
-      <c r="BO22" s="33"/>
-      <c r="BP22" s="34" t="str">
+      <c r="BM22" s="44"/>
+      <c r="BN22" s="41"/>
+      <c r="BO22" s="42"/>
+      <c r="BP22" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ22" s="44"/>
+      <c r="BQ22" s="40"/>
       <c r="BR22" s="41"/>
       <c r="BS22" s="42"/>
-      <c r="BT22" s="42" t="str">
+      <c r="BT22" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU22" s="40"/>
-      <c r="BV22" s="41"/>
-      <c r="BW22" s="42"/>
-      <c r="BX22" s="43" t="str">
+      <c r="BU22" s="31"/>
+      <c r="BV22" s="32"/>
+      <c r="BW22" s="33"/>
+      <c r="BX22" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY22" s="31"/>
-      <c r="BZ22" s="32"/>
-      <c r="CA22" s="33"/>
-      <c r="CB22" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="23" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="30">
         <v>16</v>
       </c>
@@ -5360,17 +5210,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW23" s="40"/>
+      <c r="AW23" s="44"/>
       <c r="AX23" s="41"/>
       <c r="AY23" s="42"/>
-      <c r="AZ23" s="43" t="str">
+      <c r="AZ23" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA23" s="44"/>
+      <c r="BA23" s="40"/>
       <c r="BB23" s="41"/>
       <c r="BC23" s="42"/>
-      <c r="BD23" s="42" t="str">
+      <c r="BD23" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -5381,43 +5231,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI23" s="40"/>
-      <c r="BJ23" s="41"/>
-      <c r="BK23" s="42"/>
-      <c r="BL23" s="43" t="str">
+      <c r="BI23" s="31"/>
+      <c r="BJ23" s="32"/>
+      <c r="BK23" s="33"/>
+      <c r="BL23" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM23" s="31"/>
-      <c r="BN23" s="32"/>
-      <c r="BO23" s="33"/>
-      <c r="BP23" s="34" t="str">
+      <c r="BM23" s="44"/>
+      <c r="BN23" s="41"/>
+      <c r="BO23" s="42"/>
+      <c r="BP23" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ23" s="44"/>
+      <c r="BQ23" s="40"/>
       <c r="BR23" s="41"/>
       <c r="BS23" s="42"/>
-      <c r="BT23" s="42" t="str">
+      <c r="BT23" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU23" s="40"/>
-      <c r="BV23" s="41"/>
-      <c r="BW23" s="42"/>
-      <c r="BX23" s="43" t="str">
+      <c r="BU23" s="31"/>
+      <c r="BV23" s="32"/>
+      <c r="BW23" s="33"/>
+      <c r="BX23" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY23" s="31"/>
-      <c r="BZ23" s="32"/>
-      <c r="CA23" s="33"/>
-      <c r="CB23" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="24" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30">
         <v>17</v>
       </c>
@@ -5524,17 +5367,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW24" s="40"/>
+      <c r="AW24" s="44"/>
       <c r="AX24" s="41"/>
       <c r="AY24" s="42"/>
-      <c r="AZ24" s="43" t="str">
+      <c r="AZ24" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA24" s="44"/>
+      <c r="BA24" s="40"/>
       <c r="BB24" s="41"/>
       <c r="BC24" s="42"/>
-      <c r="BD24" s="42" t="str">
+      <c r="BD24" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -5545,43 +5388,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI24" s="40"/>
-      <c r="BJ24" s="41"/>
-      <c r="BK24" s="42"/>
-      <c r="BL24" s="43" t="str">
+      <c r="BI24" s="31"/>
+      <c r="BJ24" s="32"/>
+      <c r="BK24" s="33"/>
+      <c r="BL24" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM24" s="31"/>
-      <c r="BN24" s="32"/>
-      <c r="BO24" s="33"/>
-      <c r="BP24" s="34" t="str">
+      <c r="BM24" s="44"/>
+      <c r="BN24" s="41"/>
+      <c r="BO24" s="42"/>
+      <c r="BP24" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ24" s="44"/>
+      <c r="BQ24" s="40"/>
       <c r="BR24" s="41"/>
       <c r="BS24" s="42"/>
-      <c r="BT24" s="42" t="str">
+      <c r="BT24" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU24" s="40"/>
-      <c r="BV24" s="41"/>
-      <c r="BW24" s="42"/>
-      <c r="BX24" s="43" t="str">
+      <c r="BU24" s="31"/>
+      <c r="BV24" s="32"/>
+      <c r="BW24" s="33"/>
+      <c r="BX24" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY24" s="31"/>
-      <c r="BZ24" s="32"/>
-      <c r="CA24" s="33"/>
-      <c r="CB24" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="25" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30">
         <v>18</v>
       </c>
@@ -5688,17 +5524,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW25" s="40"/>
+      <c r="AW25" s="44"/>
       <c r="AX25" s="41"/>
       <c r="AY25" s="42"/>
-      <c r="AZ25" s="43" t="str">
+      <c r="AZ25" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA25" s="44"/>
+      <c r="BA25" s="40"/>
       <c r="BB25" s="41"/>
       <c r="BC25" s="42"/>
-      <c r="BD25" s="42" t="str">
+      <c r="BD25" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -5709,43 +5545,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI25" s="40"/>
-      <c r="BJ25" s="41"/>
-      <c r="BK25" s="42"/>
-      <c r="BL25" s="43" t="str">
+      <c r="BI25" s="31"/>
+      <c r="BJ25" s="32"/>
+      <c r="BK25" s="33"/>
+      <c r="BL25" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM25" s="31"/>
-      <c r="BN25" s="32"/>
-      <c r="BO25" s="33"/>
-      <c r="BP25" s="34" t="str">
+      <c r="BM25" s="44"/>
+      <c r="BN25" s="41"/>
+      <c r="BO25" s="42"/>
+      <c r="BP25" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ25" s="44"/>
+      <c r="BQ25" s="40"/>
       <c r="BR25" s="41"/>
       <c r="BS25" s="42"/>
-      <c r="BT25" s="42" t="str">
+      <c r="BT25" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU25" s="40"/>
-      <c r="BV25" s="41"/>
-      <c r="BW25" s="42"/>
-      <c r="BX25" s="43" t="str">
+      <c r="BU25" s="31"/>
+      <c r="BV25" s="32"/>
+      <c r="BW25" s="33"/>
+      <c r="BX25" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY25" s="31"/>
-      <c r="BZ25" s="32"/>
-      <c r="CA25" s="33"/>
-      <c r="CB25" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="26" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="30">
         <v>19</v>
       </c>
@@ -5852,17 +5681,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW26" s="40"/>
+      <c r="AW26" s="44"/>
       <c r="AX26" s="41"/>
       <c r="AY26" s="42"/>
-      <c r="AZ26" s="43" t="str">
+      <c r="AZ26" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA26" s="44"/>
+      <c r="BA26" s="40"/>
       <c r="BB26" s="41"/>
       <c r="BC26" s="42"/>
-      <c r="BD26" s="42" t="str">
+      <c r="BD26" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -5873,43 +5702,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI26" s="40"/>
-      <c r="BJ26" s="41"/>
-      <c r="BK26" s="42"/>
-      <c r="BL26" s="43" t="str">
+      <c r="BI26" s="31"/>
+      <c r="BJ26" s="32"/>
+      <c r="BK26" s="33"/>
+      <c r="BL26" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM26" s="31"/>
-      <c r="BN26" s="32"/>
-      <c r="BO26" s="33"/>
-      <c r="BP26" s="34" t="str">
+      <c r="BM26" s="44"/>
+      <c r="BN26" s="41"/>
+      <c r="BO26" s="42"/>
+      <c r="BP26" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ26" s="44"/>
+      <c r="BQ26" s="40"/>
       <c r="BR26" s="41"/>
       <c r="BS26" s="42"/>
-      <c r="BT26" s="42" t="str">
+      <c r="BT26" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU26" s="40"/>
-      <c r="BV26" s="41"/>
-      <c r="BW26" s="42"/>
-      <c r="BX26" s="43" t="str">
+      <c r="BU26" s="31"/>
+      <c r="BV26" s="32"/>
+      <c r="BW26" s="33"/>
+      <c r="BX26" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY26" s="31"/>
-      <c r="BZ26" s="32"/>
-      <c r="CA26" s="33"/>
-      <c r="CB26" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="27" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30">
         <v>20</v>
       </c>
@@ -6016,17 +5838,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW27" s="40"/>
+      <c r="AW27" s="44"/>
       <c r="AX27" s="41"/>
       <c r="AY27" s="42"/>
-      <c r="AZ27" s="43" t="str">
+      <c r="AZ27" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA27" s="44"/>
+      <c r="BA27" s="40"/>
       <c r="BB27" s="41"/>
       <c r="BC27" s="42"/>
-      <c r="BD27" s="42" t="str">
+      <c r="BD27" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6037,43 +5859,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI27" s="40"/>
-      <c r="BJ27" s="41"/>
-      <c r="BK27" s="42"/>
-      <c r="BL27" s="43" t="str">
+      <c r="BI27" s="31"/>
+      <c r="BJ27" s="32"/>
+      <c r="BK27" s="33"/>
+      <c r="BL27" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM27" s="31"/>
-      <c r="BN27" s="32"/>
-      <c r="BO27" s="33"/>
-      <c r="BP27" s="34" t="str">
+      <c r="BM27" s="44"/>
+      <c r="BN27" s="41"/>
+      <c r="BO27" s="42"/>
+      <c r="BP27" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ27" s="44"/>
+      <c r="BQ27" s="40"/>
       <c r="BR27" s="41"/>
       <c r="BS27" s="42"/>
-      <c r="BT27" s="42" t="str">
+      <c r="BT27" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU27" s="40"/>
-      <c r="BV27" s="41"/>
-      <c r="BW27" s="42"/>
-      <c r="BX27" s="43" t="str">
+      <c r="BU27" s="31"/>
+      <c r="BV27" s="32"/>
+      <c r="BW27" s="33"/>
+      <c r="BX27" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY27" s="31"/>
-      <c r="BZ27" s="32"/>
-      <c r="CA27" s="33"/>
-      <c r="CB27" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="28" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="30">
         <v>21</v>
       </c>
@@ -6180,17 +5995,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW28" s="40"/>
+      <c r="AW28" s="44"/>
       <c r="AX28" s="41"/>
       <c r="AY28" s="42"/>
-      <c r="AZ28" s="43" t="str">
+      <c r="AZ28" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA28" s="44"/>
+      <c r="BA28" s="40"/>
       <c r="BB28" s="41"/>
       <c r="BC28" s="42"/>
-      <c r="BD28" s="42" t="str">
+      <c r="BD28" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6201,43 +6016,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI28" s="40"/>
-      <c r="BJ28" s="41"/>
-      <c r="BK28" s="42"/>
-      <c r="BL28" s="43" t="str">
+      <c r="BI28" s="31"/>
+      <c r="BJ28" s="32"/>
+      <c r="BK28" s="33"/>
+      <c r="BL28" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM28" s="31"/>
-      <c r="BN28" s="32"/>
-      <c r="BO28" s="33"/>
-      <c r="BP28" s="34" t="str">
+      <c r="BM28" s="44"/>
+      <c r="BN28" s="41"/>
+      <c r="BO28" s="42"/>
+      <c r="BP28" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ28" s="44"/>
+      <c r="BQ28" s="40"/>
       <c r="BR28" s="41"/>
       <c r="BS28" s="42"/>
-      <c r="BT28" s="42" t="str">
+      <c r="BT28" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU28" s="40"/>
-      <c r="BV28" s="41"/>
-      <c r="BW28" s="42"/>
-      <c r="BX28" s="43" t="str">
+      <c r="BU28" s="31"/>
+      <c r="BV28" s="32"/>
+      <c r="BW28" s="33"/>
+      <c r="BX28" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY28" s="31"/>
-      <c r="BZ28" s="32"/>
-      <c r="CA28" s="33"/>
-      <c r="CB28" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="29" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30">
         <v>22</v>
       </c>
@@ -6344,17 +6152,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW29" s="40"/>
+      <c r="AW29" s="44"/>
       <c r="AX29" s="41"/>
       <c r="AY29" s="42"/>
-      <c r="AZ29" s="43" t="str">
+      <c r="AZ29" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA29" s="44"/>
+      <c r="BA29" s="40"/>
       <c r="BB29" s="41"/>
       <c r="BC29" s="42"/>
-      <c r="BD29" s="42" t="str">
+      <c r="BD29" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6365,43 +6173,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI29" s="40"/>
-      <c r="BJ29" s="41"/>
-      <c r="BK29" s="42"/>
-      <c r="BL29" s="43" t="str">
+      <c r="BI29" s="31"/>
+      <c r="BJ29" s="32"/>
+      <c r="BK29" s="33"/>
+      <c r="BL29" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM29" s="31"/>
-      <c r="BN29" s="32"/>
-      <c r="BO29" s="33"/>
-      <c r="BP29" s="34" t="str">
+      <c r="BM29" s="44"/>
+      <c r="BN29" s="41"/>
+      <c r="BO29" s="42"/>
+      <c r="BP29" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ29" s="44"/>
+      <c r="BQ29" s="40"/>
       <c r="BR29" s="41"/>
       <c r="BS29" s="42"/>
-      <c r="BT29" s="42" t="str">
+      <c r="BT29" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU29" s="40"/>
-      <c r="BV29" s="41"/>
-      <c r="BW29" s="42"/>
-      <c r="BX29" s="43" t="str">
+      <c r="BU29" s="31"/>
+      <c r="BV29" s="32"/>
+      <c r="BW29" s="33"/>
+      <c r="BX29" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY29" s="31"/>
-      <c r="BZ29" s="32"/>
-      <c r="CA29" s="33"/>
-      <c r="CB29" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="30" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30">
         <v>23</v>
       </c>
@@ -6508,17 +6309,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW30" s="40"/>
+      <c r="AW30" s="44"/>
       <c r="AX30" s="41"/>
       <c r="AY30" s="42"/>
-      <c r="AZ30" s="43" t="str">
+      <c r="AZ30" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA30" s="44"/>
+      <c r="BA30" s="40"/>
       <c r="BB30" s="41"/>
       <c r="BC30" s="42"/>
-      <c r="BD30" s="42" t="str">
+      <c r="BD30" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6529,43 +6330,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI30" s="40"/>
-      <c r="BJ30" s="41"/>
-      <c r="BK30" s="42"/>
-      <c r="BL30" s="43" t="str">
+      <c r="BI30" s="31"/>
+      <c r="BJ30" s="32"/>
+      <c r="BK30" s="33"/>
+      <c r="BL30" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM30" s="31"/>
-      <c r="BN30" s="32"/>
-      <c r="BO30" s="33"/>
-      <c r="BP30" s="34" t="str">
+      <c r="BM30" s="44"/>
+      <c r="BN30" s="41"/>
+      <c r="BO30" s="42"/>
+      <c r="BP30" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ30" s="44"/>
+      <c r="BQ30" s="40"/>
       <c r="BR30" s="41"/>
       <c r="BS30" s="42"/>
-      <c r="BT30" s="42" t="str">
+      <c r="BT30" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU30" s="40"/>
-      <c r="BV30" s="41"/>
-      <c r="BW30" s="42"/>
-      <c r="BX30" s="43" t="str">
+      <c r="BU30" s="31"/>
+      <c r="BV30" s="32"/>
+      <c r="BW30" s="33"/>
+      <c r="BX30" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY30" s="31"/>
-      <c r="BZ30" s="32"/>
-      <c r="CA30" s="33"/>
-      <c r="CB30" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="31" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30">
         <v>24</v>
       </c>
@@ -6672,17 +6466,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW31" s="40"/>
+      <c r="AW31" s="44"/>
       <c r="AX31" s="41"/>
       <c r="AY31" s="42"/>
-      <c r="AZ31" s="43" t="str">
+      <c r="AZ31" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA31" s="44"/>
+      <c r="BA31" s="40"/>
       <c r="BB31" s="41"/>
       <c r="BC31" s="42"/>
-      <c r="BD31" s="42" t="str">
+      <c r="BD31" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6693,43 +6487,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI31" s="40"/>
-      <c r="BJ31" s="41"/>
-      <c r="BK31" s="42"/>
-      <c r="BL31" s="43" t="str">
+      <c r="BI31" s="31"/>
+      <c r="BJ31" s="32"/>
+      <c r="BK31" s="33"/>
+      <c r="BL31" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM31" s="31"/>
-      <c r="BN31" s="32"/>
-      <c r="BO31" s="33"/>
-      <c r="BP31" s="34" t="str">
+      <c r="BM31" s="44"/>
+      <c r="BN31" s="41"/>
+      <c r="BO31" s="42"/>
+      <c r="BP31" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ31" s="44"/>
+      <c r="BQ31" s="40"/>
       <c r="BR31" s="41"/>
       <c r="BS31" s="42"/>
-      <c r="BT31" s="42" t="str">
+      <c r="BT31" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU31" s="40"/>
-      <c r="BV31" s="41"/>
-      <c r="BW31" s="42"/>
-      <c r="BX31" s="43" t="str">
+      <c r="BU31" s="31"/>
+      <c r="BV31" s="32"/>
+      <c r="BW31" s="33"/>
+      <c r="BX31" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY31" s="31"/>
-      <c r="BZ31" s="32"/>
-      <c r="CA31" s="33"/>
-      <c r="CB31" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="32" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="30">
         <v>25</v>
       </c>
@@ -6836,17 +6623,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW32" s="40"/>
+      <c r="AW32" s="44"/>
       <c r="AX32" s="41"/>
       <c r="AY32" s="42"/>
-      <c r="AZ32" s="43" t="str">
+      <c r="AZ32" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA32" s="44"/>
+      <c r="BA32" s="40"/>
       <c r="BB32" s="41"/>
       <c r="BC32" s="42"/>
-      <c r="BD32" s="42" t="str">
+      <c r="BD32" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6857,43 +6644,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI32" s="40"/>
-      <c r="BJ32" s="41"/>
-      <c r="BK32" s="42"/>
-      <c r="BL32" s="43" t="str">
+      <c r="BI32" s="31"/>
+      <c r="BJ32" s="32"/>
+      <c r="BK32" s="33"/>
+      <c r="BL32" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM32" s="31"/>
-      <c r="BN32" s="32"/>
-      <c r="BO32" s="33"/>
-      <c r="BP32" s="34" t="str">
+      <c r="BM32" s="44"/>
+      <c r="BN32" s="41"/>
+      <c r="BO32" s="42"/>
+      <c r="BP32" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ32" s="44"/>
+      <c r="BQ32" s="40"/>
       <c r="BR32" s="41"/>
       <c r="BS32" s="42"/>
-      <c r="BT32" s="42" t="str">
+      <c r="BT32" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU32" s="40"/>
-      <c r="BV32" s="41"/>
-      <c r="BW32" s="42"/>
-      <c r="BX32" s="43" t="str">
+      <c r="BU32" s="31"/>
+      <c r="BV32" s="32"/>
+      <c r="BW32" s="33"/>
+      <c r="BX32" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY32" s="31"/>
-      <c r="BZ32" s="32"/>
-      <c r="CA32" s="33"/>
-      <c r="CB32" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="33" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="30">
         <v>26</v>
       </c>
@@ -7000,17 +6780,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW33" s="40"/>
+      <c r="AW33" s="44"/>
       <c r="AX33" s="41"/>
       <c r="AY33" s="42"/>
-      <c r="AZ33" s="43" t="str">
+      <c r="AZ33" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA33" s="44"/>
+      <c r="BA33" s="40"/>
       <c r="BB33" s="41"/>
       <c r="BC33" s="42"/>
-      <c r="BD33" s="42" t="str">
+      <c r="BD33" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7021,43 +6801,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI33" s="40"/>
-      <c r="BJ33" s="41"/>
-      <c r="BK33" s="42"/>
-      <c r="BL33" s="43" t="str">
+      <c r="BI33" s="31"/>
+      <c r="BJ33" s="32"/>
+      <c r="BK33" s="33"/>
+      <c r="BL33" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM33" s="31"/>
-      <c r="BN33" s="32"/>
-      <c r="BO33" s="33"/>
-      <c r="BP33" s="34" t="str">
+      <c r="BM33" s="44"/>
+      <c r="BN33" s="41"/>
+      <c r="BO33" s="42"/>
+      <c r="BP33" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ33" s="44"/>
+      <c r="BQ33" s="40"/>
       <c r="BR33" s="41"/>
       <c r="BS33" s="42"/>
-      <c r="BT33" s="42" t="str">
+      <c r="BT33" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU33" s="40"/>
-      <c r="BV33" s="41"/>
-      <c r="BW33" s="42"/>
-      <c r="BX33" s="43" t="str">
+      <c r="BU33" s="31"/>
+      <c r="BV33" s="32"/>
+      <c r="BW33" s="33"/>
+      <c r="BX33" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY33" s="31"/>
-      <c r="BZ33" s="32"/>
-      <c r="CA33" s="33"/>
-      <c r="CB33" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="34" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="30">
         <v>27</v>
       </c>
@@ -7164,17 +6937,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW34" s="40"/>
+      <c r="AW34" s="44"/>
       <c r="AX34" s="41"/>
       <c r="AY34" s="42"/>
-      <c r="AZ34" s="43" t="str">
+      <c r="AZ34" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA34" s="44"/>
+      <c r="BA34" s="40"/>
       <c r="BB34" s="41"/>
       <c r="BC34" s="42"/>
-      <c r="BD34" s="42" t="str">
+      <c r="BD34" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7185,43 +6958,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI34" s="40"/>
-      <c r="BJ34" s="41"/>
-      <c r="BK34" s="42"/>
-      <c r="BL34" s="43" t="str">
+      <c r="BI34" s="31"/>
+      <c r="BJ34" s="32"/>
+      <c r="BK34" s="33"/>
+      <c r="BL34" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM34" s="31"/>
-      <c r="BN34" s="32"/>
-      <c r="BO34" s="33"/>
-      <c r="BP34" s="34" t="str">
+      <c r="BM34" s="44"/>
+      <c r="BN34" s="41"/>
+      <c r="BO34" s="42"/>
+      <c r="BP34" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ34" s="44"/>
+      <c r="BQ34" s="40"/>
       <c r="BR34" s="41"/>
       <c r="BS34" s="42"/>
-      <c r="BT34" s="42" t="str">
+      <c r="BT34" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU34" s="40"/>
-      <c r="BV34" s="41"/>
-      <c r="BW34" s="42"/>
-      <c r="BX34" s="43" t="str">
+      <c r="BU34" s="31"/>
+      <c r="BV34" s="32"/>
+      <c r="BW34" s="33"/>
+      <c r="BX34" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY34" s="31"/>
-      <c r="BZ34" s="32"/>
-      <c r="CA34" s="33"/>
-      <c r="CB34" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="35" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="30">
         <v>28</v>
       </c>
@@ -7328,17 +7094,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW35" s="40"/>
+      <c r="AW35" s="44"/>
       <c r="AX35" s="41"/>
       <c r="AY35" s="42"/>
-      <c r="AZ35" s="43" t="str">
+      <c r="AZ35" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA35" s="44"/>
+      <c r="BA35" s="40"/>
       <c r="BB35" s="41"/>
       <c r="BC35" s="42"/>
-      <c r="BD35" s="42" t="str">
+      <c r="BD35" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7349,43 +7115,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI35" s="40"/>
-      <c r="BJ35" s="41"/>
-      <c r="BK35" s="42"/>
-      <c r="BL35" s="43" t="str">
+      <c r="BI35" s="31"/>
+      <c r="BJ35" s="32"/>
+      <c r="BK35" s="33"/>
+      <c r="BL35" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM35" s="31"/>
-      <c r="BN35" s="32"/>
-      <c r="BO35" s="33"/>
-      <c r="BP35" s="34" t="str">
+      <c r="BM35" s="44"/>
+      <c r="BN35" s="41"/>
+      <c r="BO35" s="42"/>
+      <c r="BP35" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ35" s="44"/>
+      <c r="BQ35" s="40"/>
       <c r="BR35" s="41"/>
       <c r="BS35" s="42"/>
-      <c r="BT35" s="42" t="str">
+      <c r="BT35" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU35" s="40"/>
-      <c r="BV35" s="41"/>
-      <c r="BW35" s="42"/>
-      <c r="BX35" s="43" t="str">
+      <c r="BU35" s="31"/>
+      <c r="BV35" s="32"/>
+      <c r="BW35" s="33"/>
+      <c r="BX35" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY35" s="31"/>
-      <c r="BZ35" s="32"/>
-      <c r="CA35" s="33"/>
-      <c r="CB35" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="36" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="30">
         <v>29</v>
       </c>
@@ -7492,17 +7251,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW36" s="40"/>
+      <c r="AW36" s="44"/>
       <c r="AX36" s="41"/>
       <c r="AY36" s="42"/>
-      <c r="AZ36" s="43" t="str">
+      <c r="AZ36" s="42" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA36" s="44"/>
+      <c r="BA36" s="40"/>
       <c r="BB36" s="41"/>
       <c r="BC36" s="42"/>
-      <c r="BD36" s="42" t="str">
+      <c r="BD36" s="43" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7513,43 +7272,36 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI36" s="40"/>
-      <c r="BJ36" s="41"/>
-      <c r="BK36" s="42"/>
-      <c r="BL36" s="43" t="str">
+      <c r="BI36" s="31"/>
+      <c r="BJ36" s="32"/>
+      <c r="BK36" s="33"/>
+      <c r="BL36" s="34" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM36" s="31"/>
-      <c r="BN36" s="32"/>
-      <c r="BO36" s="33"/>
-      <c r="BP36" s="34" t="str">
+      <c r="BM36" s="44"/>
+      <c r="BN36" s="41"/>
+      <c r="BO36" s="42"/>
+      <c r="BP36" s="42" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ36" s="44"/>
+      <c r="BQ36" s="40"/>
       <c r="BR36" s="41"/>
       <c r="BS36" s="42"/>
-      <c r="BT36" s="42" t="str">
+      <c r="BT36" s="43" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU36" s="40"/>
-      <c r="BV36" s="41"/>
-      <c r="BW36" s="42"/>
-      <c r="BX36" s="43" t="str">
+      <c r="BU36" s="31"/>
+      <c r="BV36" s="32"/>
+      <c r="BW36" s="33"/>
+      <c r="BX36" s="34" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY36" s="31"/>
-      <c r="BZ36" s="32"/>
-      <c r="CA36" s="33"/>
-      <c r="CB36" s="34" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="37" spans="1:80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45">
         <v>30</v>
       </c>
@@ -7656,17 +7408,17 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AW37" s="55"/>
+      <c r="AW37" s="59"/>
       <c r="AX37" s="56"/>
       <c r="AY37" s="57"/>
-      <c r="AZ37" s="58" t="str">
+      <c r="AZ37" s="57" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="BA37" s="59"/>
+      <c r="BA37" s="55"/>
       <c r="BB37" s="56"/>
       <c r="BC37" s="57"/>
-      <c r="BD37" s="57" t="str">
+      <c r="BD37" s="58" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7677,61 +7429,54 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="BI37" s="55"/>
-      <c r="BJ37" s="56"/>
-      <c r="BK37" s="57"/>
-      <c r="BL37" s="58" t="str">
+      <c r="BI37" s="46"/>
+      <c r="BJ37" s="47"/>
+      <c r="BK37" s="48"/>
+      <c r="BL37" s="49" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="BM37" s="46"/>
-      <c r="BN37" s="47"/>
-      <c r="BO37" s="48"/>
-      <c r="BP37" s="49" t="str">
+      <c r="BM37" s="59"/>
+      <c r="BN37" s="56"/>
+      <c r="BO37" s="57"/>
+      <c r="BP37" s="57" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="BQ37" s="59"/>
+      <c r="BQ37" s="55"/>
       <c r="BR37" s="56"/>
       <c r="BS37" s="57"/>
-      <c r="BT37" s="57" t="str">
+      <c r="BT37" s="58" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="BU37" s="55"/>
-      <c r="BV37" s="56"/>
-      <c r="BW37" s="57"/>
-      <c r="BX37" s="58" t="str">
+      <c r="BU37" s="46"/>
+      <c r="BV37" s="47"/>
+      <c r="BW37" s="48"/>
+      <c r="BX37" s="49" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="BY37" s="46"/>
-      <c r="BZ37" s="47"/>
-      <c r="CA37" s="48"/>
-      <c r="CB37" s="49" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
     </row>
-    <row r="38" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="127" t="s">
+    <row r="38" spans="1:76" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="128"/>
+      <c r="B38" s="112"/>
       <c r="C38" s="65" t="str">
         <f>IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
         <v/>
       </c>
       <c r="D38" s="66" t="str">
-        <f t="shared" ref="D38:E38" si="29">IF(SUM(D8:D37)=0,"",AVERAGE(D8:D37))</f>
+        <f t="shared" ref="D38:E38" si="28">IF(SUM(D8:D37)=0,"",AVERAGE(D8:D37))</f>
         <v/>
       </c>
       <c r="E38" s="67" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="F38" s="68" t="str">
-        <f t="shared" ref="F38:AP38" si="30">IF(SUM(F8:F37)=0,"",AVERAGE(F8:F37))</f>
+        <f t="shared" ref="F38:AP38" si="29">IF(SUM(F8:F37)=0,"",AVERAGE(F8:F37))</f>
         <v/>
       </c>
       <c r="G38" s="65" t="str">
@@ -7739,15 +7484,15 @@
         <v/>
       </c>
       <c r="H38" s="66" t="str">
-        <f t="shared" ref="H38:I38" si="31">IF(SUM(H8:H37)=0,"",AVERAGE(H8:H37))</f>
+        <f t="shared" ref="H38:I38" si="30">IF(SUM(H8:H37)=0,"",AVERAGE(H8:H37))</f>
         <v/>
       </c>
       <c r="I38" s="67" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J38" s="68" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K38" s="69" t="str">
@@ -7755,15 +7500,15 @@
         <v/>
       </c>
       <c r="L38" s="66" t="str">
-        <f t="shared" ref="L38:M38" si="32">IF(SUM(L8:L37)=0,"",AVERAGE(L8:L37))</f>
+        <f t="shared" ref="L38:M38" si="31">IF(SUM(L8:L37)=0,"",AVERAGE(L8:L37))</f>
         <v/>
       </c>
       <c r="M38" s="67" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N38" s="67" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O38" s="65" t="str">
@@ -7771,15 +7516,15 @@
         <v/>
       </c>
       <c r="P38" s="66" t="str">
-        <f t="shared" ref="P38:Q38" si="33">IF(SUM(P8:P37)=0,"",AVERAGE(P8:P37))</f>
+        <f t="shared" ref="P38:Q38" si="32">IF(SUM(P8:P37)=0,"",AVERAGE(P8:P37))</f>
         <v/>
       </c>
       <c r="Q38" s="67" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="R38" s="68" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="S38" s="65" t="str">
@@ -7787,15 +7532,15 @@
         <v/>
       </c>
       <c r="T38" s="66" t="str">
-        <f t="shared" ref="T38:U38" si="34">IF(SUM(T8:T37)=0,"",AVERAGE(T8:T37))</f>
+        <f t="shared" ref="T38:U38" si="33">IF(SUM(T8:T37)=0,"",AVERAGE(T8:T37))</f>
         <v/>
       </c>
       <c r="U38" s="67" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="V38" s="68" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="W38" s="69" t="str">
@@ -7803,15 +7548,15 @@
         <v/>
       </c>
       <c r="X38" s="66" t="str">
-        <f t="shared" ref="X38:Y38" si="35">IF(SUM(X8:X37)=0,"",AVERAGE(X8:X37))</f>
+        <f t="shared" ref="X38:Y38" si="34">IF(SUM(X8:X37)=0,"",AVERAGE(X8:X37))</f>
         <v/>
       </c>
       <c r="Y38" s="67" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Z38" s="67" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AA38" s="65" t="str">
@@ -7819,15 +7564,15 @@
         <v/>
       </c>
       <c r="AB38" s="66" t="str">
-        <f t="shared" ref="AB38:AC38" si="36">IF(SUM(AB8:AB37)=0,"",AVERAGE(AB8:AB37))</f>
+        <f t="shared" ref="AB38:AC38" si="35">IF(SUM(AB8:AB37)=0,"",AVERAGE(AB8:AB37))</f>
         <v/>
       </c>
       <c r="AC38" s="67" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AD38" s="68" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AE38" s="70" t="str">
@@ -7835,15 +7580,15 @@
         <v/>
       </c>
       <c r="AF38" s="71" t="str">
-        <f t="shared" ref="AF38:AG38" si="37">IF(SUM(AF8:AF37)=0,"",AVERAGE(AF8:AF37))</f>
+        <f t="shared" ref="AF38:AG38" si="36">IF(SUM(AF8:AF37)=0,"",AVERAGE(AF8:AF37))</f>
         <v/>
       </c>
       <c r="AG38" s="72" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="AH38" s="73" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AI38" s="69" t="str">
@@ -7851,15 +7596,15 @@
         <v/>
       </c>
       <c r="AJ38" s="66" t="str">
-        <f t="shared" ref="AJ38:AK38" si="38">IF(SUM(AJ8:AJ37)=0,"",AVERAGE(AJ8:AJ37))</f>
+        <f t="shared" ref="AJ38:AK38" si="37">IF(SUM(AJ8:AJ37)=0,"",AVERAGE(AJ8:AJ37))</f>
         <v/>
       </c>
       <c r="AK38" s="67" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AL38" s="67" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AM38" s="74" t="str">
@@ -7867,67 +7612,67 @@
         <v/>
       </c>
       <c r="AN38" s="75" t="str">
-        <f t="shared" ref="AN38:AO38" si="39">IF(SUM(AN8:AN37)=0,"",AVERAGE(AN8:AN37))</f>
+        <f t="shared" ref="AN38:AO38" si="38">IF(SUM(AN8:AN37)=0,"",AVERAGE(AN8:AN37))</f>
         <v/>
       </c>
       <c r="AO38" s="76" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AP38" s="77" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AQ38" s="127" t="s">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AQ38" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="AR38" s="128"/>
+      <c r="AR38" s="112"/>
       <c r="AS38" s="78" t="str">
         <f>IF(SUM(AS8:AS37)=0,"",AVERAGE(AS8:AS37))</f>
         <v/>
       </c>
       <c r="AT38" s="79" t="str">
-        <f t="shared" ref="AT38:AU38" si="40">IF(SUM(AT8:AT37)=0,"",AVERAGE(AT8:AT37))</f>
+        <f t="shared" ref="AT38:AU38" si="39">IF(SUM(AT8:AT37)=0,"",AVERAGE(AT8:AT37))</f>
         <v/>
       </c>
       <c r="AU38" s="80" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="AV38" s="81" t="str">
-        <f t="shared" ref="AV38" si="41">IF(SUM(AV8:AV37)=0,"",AVERAGE(AV8:AV37))</f>
-        <v/>
-      </c>
-      <c r="AW38" s="78" t="str">
+        <f t="shared" ref="AV38" si="40">IF(SUM(AV8:AV37)=0,"",AVERAGE(AV8:AV37))</f>
+        <v/>
+      </c>
+      <c r="AW38" s="82" t="str">
         <f>IF(SUM(AW8:AW37)=0,"",AVERAGE(AW8:AW37))</f>
         <v/>
       </c>
       <c r="AX38" s="79" t="str">
-        <f t="shared" ref="AX38:AY38" si="42">IF(SUM(AX8:AX37)=0,"",AVERAGE(AX8:AX37))</f>
+        <f t="shared" ref="AX38:AY38" si="41">IF(SUM(AX8:AX37)=0,"",AVERAGE(AX8:AX37))</f>
         <v/>
       </c>
       <c r="AY38" s="80" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="AZ38" s="81" t="str">
-        <f t="shared" ref="AZ38" si="43">IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
-        <v/>
-      </c>
-      <c r="BA38" s="82" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AZ38" s="80" t="str">
+        <f t="shared" ref="AZ38" si="42">IF(SUM(AZ8:AZ37)=0,"",AVERAGE(AZ8:AZ37))</f>
+        <v/>
+      </c>
+      <c r="BA38" s="78" t="str">
         <f>IF(SUM(BA8:BA37)=0,"",AVERAGE(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB38" s="79" t="str">
-        <f t="shared" ref="BB38:BC38" si="44">IF(SUM(BB8:BB37)=0,"",AVERAGE(BB8:BB37))</f>
+        <f t="shared" ref="BB38:BC38" si="43">IF(SUM(BB8:BB37)=0,"",AVERAGE(BB8:BB37))</f>
         <v/>
       </c>
       <c r="BC38" s="80" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="BD38" s="80" t="str">
-        <f t="shared" ref="BD38" si="45">IF(SUM(BD8:BD37)=0,"",AVERAGE(BD8:BD37))</f>
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="BD38" s="81" t="str">
+        <f t="shared" ref="BD38" si="44">IF(SUM(BD8:BD37)=0,"",AVERAGE(BD8:BD37))</f>
         <v/>
       </c>
       <c r="BE38" s="78" t="str">
@@ -7935,117 +7680,101 @@
         <v/>
       </c>
       <c r="BF38" s="79" t="str">
-        <f t="shared" ref="BF38:BG38" si="46">IF(SUM(BF8:BF37)=0,"",AVERAGE(BF8:BF37))</f>
+        <f t="shared" ref="BF38:BG38" si="45">IF(SUM(BF8:BF37)=0,"",AVERAGE(BF8:BF37))</f>
         <v/>
       </c>
       <c r="BG38" s="80" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BH38" s="81" t="str">
-        <f t="shared" ref="BH38" si="47">IF(SUM(BH8:BH37)=0,"",AVERAGE(BH8:BH37))</f>
-        <v/>
-      </c>
-      <c r="BI38" s="78" t="str">
+        <f t="shared" ref="BH38" si="46">IF(SUM(BH8:BH37)=0,"",AVERAGE(BH8:BH37))</f>
+        <v/>
+      </c>
+      <c r="BI38" s="65" t="str">
         <f>IF(SUM(BI8:BI37)=0,"",AVERAGE(BI8:BI37))</f>
         <v/>
       </c>
-      <c r="BJ38" s="79" t="str">
-        <f t="shared" ref="BJ38:BK38" si="48">IF(SUM(BJ8:BJ37)=0,"",AVERAGE(BJ8:BJ37))</f>
-        <v/>
-      </c>
-      <c r="BK38" s="80" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="BL38" s="81" t="str">
-        <f t="shared" ref="BL38" si="49">IF(SUM(BL8:BL37)=0,"",AVERAGE(BL8:BL37))</f>
-        <v/>
-      </c>
-      <c r="BM38" s="65" t="str">
+      <c r="BJ38" s="66" t="str">
+        <f t="shared" ref="BJ38:BK38" si="47">IF(SUM(BJ8:BJ37)=0,"",AVERAGE(BJ8:BJ37))</f>
+        <v/>
+      </c>
+      <c r="BK38" s="67" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="BL38" s="68" t="str">
+        <f t="shared" ref="BL38" si="48">IF(SUM(BL8:BL37)=0,"",AVERAGE(BL8:BL37))</f>
+        <v/>
+      </c>
+      <c r="BM38" s="82" t="str">
         <f>IF(SUM(BM8:BM37)=0,"",AVERAGE(BM8:BM37))</f>
         <v/>
       </c>
-      <c r="BN38" s="66" t="str">
-        <f t="shared" ref="BN38:BO38" si="50">IF(SUM(BN8:BN37)=0,"",AVERAGE(BN8:BN37))</f>
-        <v/>
-      </c>
-      <c r="BO38" s="67" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BP38" s="68" t="str">
-        <f t="shared" ref="BP38" si="51">IF(SUM(BP8:BP37)=0,"",AVERAGE(BP8:BP37))</f>
-        <v/>
-      </c>
-      <c r="BQ38" s="82" t="str">
+      <c r="BN38" s="79" t="str">
+        <f t="shared" ref="BN38:BO38" si="49">IF(SUM(BN8:BN37)=0,"",AVERAGE(BN8:BN37))</f>
+        <v/>
+      </c>
+      <c r="BO38" s="80" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="BP38" s="80" t="str">
+        <f t="shared" ref="BP38" si="50">IF(SUM(BP8:BP37)=0,"",AVERAGE(BP8:BP37))</f>
+        <v/>
+      </c>
+      <c r="BQ38" s="78" t="str">
         <f>IF(SUM(BQ8:BQ37)=0,"",AVERAGE(BQ8:BQ37))</f>
         <v/>
       </c>
       <c r="BR38" s="79" t="str">
-        <f t="shared" ref="BR38:BS38" si="52">IF(SUM(BR8:BR37)=0,"",AVERAGE(BR8:BR37))</f>
+        <f t="shared" ref="BR38:BS38" si="51">IF(SUM(BR8:BR37)=0,"",AVERAGE(BR8:BR37))</f>
         <v/>
       </c>
       <c r="BS38" s="80" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="BT38" s="80" t="str">
-        <f t="shared" ref="BT38" si="53">IF(SUM(BT8:BT37)=0,"",AVERAGE(BT8:BT37))</f>
-        <v/>
-      </c>
-      <c r="BU38" s="78" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="BT38" s="81" t="str">
+        <f t="shared" ref="BT38" si="52">IF(SUM(BT8:BT37)=0,"",AVERAGE(BT8:BT37))</f>
+        <v/>
+      </c>
+      <c r="BU38" s="70" t="str">
         <f>IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
         <v/>
       </c>
-      <c r="BV38" s="79" t="str">
-        <f t="shared" ref="BV38:BW38" si="54">IF(SUM(BV8:BV37)=0,"",AVERAGE(BV8:BV37))</f>
-        <v/>
-      </c>
-      <c r="BW38" s="80" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BX38" s="81" t="str">
-        <f t="shared" ref="BX38" si="55">IF(SUM(BX8:BX37)=0,"",AVERAGE(BX8:BX37))</f>
-        <v/>
-      </c>
-      <c r="BY38" s="70" t="str">
-        <f>IF(SUM(BY8:BY37)=0,"",AVERAGE(BY8:BY37))</f>
-        <v/>
-      </c>
-      <c r="BZ38" s="71" t="str">
-        <f t="shared" ref="BZ38:CA38" si="56">IF(SUM(BZ8:BZ37)=0,"",AVERAGE(BZ8:BZ37))</f>
-        <v/>
-      </c>
-      <c r="CA38" s="72" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CB38" s="73" t="str">
-        <f t="shared" ref="CB38" si="57">IF(SUM(CB8:CB37)=0,"",AVERAGE(CB8:CB37))</f>
+      <c r="BV38" s="71" t="str">
+        <f t="shared" ref="BV38:BW38" si="53">IF(SUM(BV8:BV37)=0,"",AVERAGE(BV8:BV37))</f>
+        <v/>
+      </c>
+      <c r="BW38" s="72" t="str">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
+      <c r="BX38" s="73" t="str">
+        <f t="shared" ref="BX38" si="54">IF(SUM(BX8:BX37)=0,"",AVERAGE(BX8:BX37))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="114" t="s">
+    <row r="39" spans="1:76" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="115"/>
+      <c r="B39" s="114"/>
       <c r="C39" s="65" t="str">
         <f>IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
         <v/>
       </c>
       <c r="D39" s="66" t="str">
-        <f t="shared" ref="D39:E39" si="58">IF(SUM(D8:D37)=0,"",MEDIAN(D8:D37))</f>
+        <f t="shared" ref="D39:E39" si="55">IF(SUM(D8:D37)=0,"",MEDIAN(D8:D37))</f>
         <v/>
       </c>
       <c r="E39" s="67" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="F39" s="68" t="str">
-        <f t="shared" ref="F39:AP39" si="59">IF(SUM(F8:F37)=0,"",MEDIAN(F8:F37))</f>
+        <f t="shared" ref="F39:AP39" si="56">IF(SUM(F8:F37)=0,"",MEDIAN(F8:F37))</f>
         <v/>
       </c>
       <c r="G39" s="65" t="str">
@@ -8053,15 +7782,15 @@
         <v/>
       </c>
       <c r="H39" s="66" t="str">
-        <f t="shared" ref="H39:I39" si="60">IF(SUM(H8:H37)=0,"",MEDIAN(H8:H37))</f>
+        <f t="shared" ref="H39:I39" si="57">IF(SUM(H8:H37)=0,"",MEDIAN(H8:H37))</f>
         <v/>
       </c>
       <c r="I39" s="67" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="J39" s="68" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="K39" s="69" t="str">
@@ -8069,15 +7798,15 @@
         <v/>
       </c>
       <c r="L39" s="66" t="str">
-        <f t="shared" ref="L39:M39" si="61">IF(SUM(L8:L37)=0,"",MEDIAN(L8:L37))</f>
+        <f t="shared" ref="L39:M39" si="58">IF(SUM(L8:L37)=0,"",MEDIAN(L8:L37))</f>
         <v/>
       </c>
       <c r="M39" s="67" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="N39" s="67" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="O39" s="65" t="str">
@@ -8085,15 +7814,15 @@
         <v/>
       </c>
       <c r="P39" s="66" t="str">
-        <f t="shared" ref="P39:Q39" si="62">IF(SUM(P8:P37)=0,"",MEDIAN(P8:P37))</f>
+        <f t="shared" ref="P39:Q39" si="59">IF(SUM(P8:P37)=0,"",MEDIAN(P8:P37))</f>
         <v/>
       </c>
       <c r="Q39" s="67" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="R39" s="68" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="S39" s="65" t="str">
@@ -8101,15 +7830,15 @@
         <v/>
       </c>
       <c r="T39" s="66" t="str">
-        <f t="shared" ref="T39:U39" si="63">IF(SUM(T8:T37)=0,"",MEDIAN(T8:T37))</f>
+        <f t="shared" ref="T39:U39" si="60">IF(SUM(T8:T37)=0,"",MEDIAN(T8:T37))</f>
         <v/>
       </c>
       <c r="U39" s="67" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="V39" s="68" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="W39" s="69" t="str">
@@ -8117,15 +7846,15 @@
         <v/>
       </c>
       <c r="X39" s="66" t="str">
-        <f t="shared" ref="X39:Y39" si="64">IF(SUM(X8:X37)=0,"",MEDIAN(X8:X37))</f>
+        <f t="shared" ref="X39:Y39" si="61">IF(SUM(X8:X37)=0,"",MEDIAN(X8:X37))</f>
         <v/>
       </c>
       <c r="Y39" s="67" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="Z39" s="67" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="AA39" s="65" t="str">
@@ -8133,15 +7862,15 @@
         <v/>
       </c>
       <c r="AB39" s="66" t="str">
-        <f t="shared" ref="AB39:AC39" si="65">IF(SUM(AB8:AB37)=0,"",MEDIAN(AB8:AB37))</f>
+        <f t="shared" ref="AB39:AC39" si="62">IF(SUM(AB8:AB37)=0,"",MEDIAN(AB8:AB37))</f>
         <v/>
       </c>
       <c r="AC39" s="67" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AD39" s="68" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="AE39" s="65" t="str">
@@ -8149,15 +7878,15 @@
         <v/>
       </c>
       <c r="AF39" s="66" t="str">
-        <f t="shared" ref="AF39:AG39" si="66">IF(SUM(AF8:AF37)=0,"",MEDIAN(AF8:AF37))</f>
+        <f t="shared" ref="AF39:AG39" si="63">IF(SUM(AF8:AF37)=0,"",MEDIAN(AF8:AF37))</f>
         <v/>
       </c>
       <c r="AG39" s="67" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="AH39" s="68" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="AI39" s="69" t="str">
@@ -8165,15 +7894,15 @@
         <v/>
       </c>
       <c r="AJ39" s="66" t="str">
-        <f t="shared" ref="AJ39:AK39" si="67">IF(SUM(AJ8:AJ37)=0,"",MEDIAN(AJ8:AJ37))</f>
+        <f t="shared" ref="AJ39:AK39" si="64">IF(SUM(AJ8:AJ37)=0,"",MEDIAN(AJ8:AJ37))</f>
         <v/>
       </c>
       <c r="AK39" s="67" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="AL39" s="67" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="AM39" s="74" t="str">
@@ -8181,67 +7910,67 @@
         <v/>
       </c>
       <c r="AN39" s="75" t="str">
-        <f t="shared" ref="AN39:AO39" si="68">IF(SUM(AN8:AN37)=0,"",MEDIAN(AN8:AN37))</f>
+        <f t="shared" ref="AN39:AO39" si="65">IF(SUM(AN8:AN37)=0,"",MEDIAN(AN8:AN37))</f>
         <v/>
       </c>
       <c r="AO39" s="76" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="AP39" s="77" t="str">
-        <f t="shared" si="59"/>
-        <v/>
-      </c>
-      <c r="AQ39" s="114" t="s">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="AQ39" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="AR39" s="115"/>
+      <c r="AR39" s="114"/>
       <c r="AS39" s="78" t="str">
         <f>IF(SUM(AS8:AS37)=0,"",MEDIAN(AS8:AS37))</f>
         <v/>
       </c>
       <c r="AT39" s="79" t="str">
-        <f t="shared" ref="AT39:AU39" si="69">IF(SUM(AT8:AT37)=0,"",MEDIAN(AT8:AT37))</f>
+        <f t="shared" ref="AT39:AU39" si="66">IF(SUM(AT8:AT37)=0,"",MEDIAN(AT8:AT37))</f>
         <v/>
       </c>
       <c r="AU39" s="80" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="AV39" s="81" t="str">
-        <f t="shared" ref="AV39" si="70">IF(SUM(AV8:AV37)=0,"",MEDIAN(AV8:AV37))</f>
-        <v/>
-      </c>
-      <c r="AW39" s="78" t="str">
+        <f t="shared" ref="AV39" si="67">IF(SUM(AV8:AV37)=0,"",MEDIAN(AV8:AV37))</f>
+        <v/>
+      </c>
+      <c r="AW39" s="82" t="str">
         <f>IF(SUM(AW8:AW37)=0,"",MEDIAN(AW8:AW37))</f>
         <v/>
       </c>
       <c r="AX39" s="79" t="str">
-        <f t="shared" ref="AX39:AY39" si="71">IF(SUM(AX8:AX37)=0,"",MEDIAN(AX8:AX37))</f>
+        <f t="shared" ref="AX39:AY39" si="68">IF(SUM(AX8:AX37)=0,"",MEDIAN(AX8:AX37))</f>
         <v/>
       </c>
       <c r="AY39" s="80" t="str">
-        <f t="shared" si="71"/>
-        <v/>
-      </c>
-      <c r="AZ39" s="81" t="str">
-        <f t="shared" ref="AZ39" si="72">IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
-        <v/>
-      </c>
-      <c r="BA39" s="82" t="str">
+        <f t="shared" si="68"/>
+        <v/>
+      </c>
+      <c r="AZ39" s="80" t="str">
+        <f t="shared" ref="AZ39" si="69">IF(SUM(AZ8:AZ37)=0,"",MEDIAN(AZ8:AZ37))</f>
+        <v/>
+      </c>
+      <c r="BA39" s="78" t="str">
         <f>IF(SUM(BA8:BA37)=0,"",MEDIAN(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB39" s="79" t="str">
-        <f t="shared" ref="BB39:BC39" si="73">IF(SUM(BB8:BB37)=0,"",MEDIAN(BB8:BB37))</f>
+        <f t="shared" ref="BB39:BC39" si="70">IF(SUM(BB8:BB37)=0,"",MEDIAN(BB8:BB37))</f>
         <v/>
       </c>
       <c r="BC39" s="80" t="str">
-        <f t="shared" si="73"/>
-        <v/>
-      </c>
-      <c r="BD39" s="80" t="str">
-        <f t="shared" ref="BD39" si="74">IF(SUM(BD8:BD37)=0,"",MEDIAN(BD8:BD37))</f>
+        <f t="shared" si="70"/>
+        <v/>
+      </c>
+      <c r="BD39" s="81" t="str">
+        <f t="shared" ref="BD39" si="71">IF(SUM(BD8:BD37)=0,"",MEDIAN(BD8:BD37))</f>
         <v/>
       </c>
       <c r="BE39" s="78" t="str">
@@ -8249,117 +7978,101 @@
         <v/>
       </c>
       <c r="BF39" s="79" t="str">
-        <f t="shared" ref="BF39:BG39" si="75">IF(SUM(BF8:BF37)=0,"",MEDIAN(BF8:BF37))</f>
+        <f t="shared" ref="BF39:BG39" si="72">IF(SUM(BF8:BF37)=0,"",MEDIAN(BF8:BF37))</f>
         <v/>
       </c>
       <c r="BG39" s="80" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="BH39" s="81" t="str">
-        <f t="shared" ref="BH39" si="76">IF(SUM(BH8:BH37)=0,"",MEDIAN(BH8:BH37))</f>
-        <v/>
-      </c>
-      <c r="BI39" s="78" t="str">
+        <f t="shared" ref="BH39" si="73">IF(SUM(BH8:BH37)=0,"",MEDIAN(BH8:BH37))</f>
+        <v/>
+      </c>
+      <c r="BI39" s="65" t="str">
         <f>IF(SUM(BI8:BI37)=0,"",MEDIAN(BI8:BI37))</f>
         <v/>
       </c>
-      <c r="BJ39" s="79" t="str">
-        <f t="shared" ref="BJ39:BK39" si="77">IF(SUM(BJ8:BJ37)=0,"",MEDIAN(BJ8:BJ37))</f>
-        <v/>
-      </c>
-      <c r="BK39" s="80" t="str">
-        <f t="shared" si="77"/>
-        <v/>
-      </c>
-      <c r="BL39" s="81" t="str">
-        <f t="shared" ref="BL39" si="78">IF(SUM(BL8:BL37)=0,"",MEDIAN(BL8:BL37))</f>
-        <v/>
-      </c>
-      <c r="BM39" s="65" t="str">
+      <c r="BJ39" s="66" t="str">
+        <f t="shared" ref="BJ39:BK39" si="74">IF(SUM(BJ8:BJ37)=0,"",MEDIAN(BJ8:BJ37))</f>
+        <v/>
+      </c>
+      <c r="BK39" s="67" t="str">
+        <f t="shared" si="74"/>
+        <v/>
+      </c>
+      <c r="BL39" s="68" t="str">
+        <f t="shared" ref="BL39" si="75">IF(SUM(BL8:BL37)=0,"",MEDIAN(BL8:BL37))</f>
+        <v/>
+      </c>
+      <c r="BM39" s="82" t="str">
         <f>IF(SUM(BM8:BM37)=0,"",MEDIAN(BM8:BM37))</f>
         <v/>
       </c>
-      <c r="BN39" s="66" t="str">
-        <f t="shared" ref="BN39:BO39" si="79">IF(SUM(BN8:BN37)=0,"",MEDIAN(BN8:BN37))</f>
-        <v/>
-      </c>
-      <c r="BO39" s="67" t="str">
-        <f t="shared" si="79"/>
-        <v/>
-      </c>
-      <c r="BP39" s="68" t="str">
-        <f t="shared" ref="BP39" si="80">IF(SUM(BP8:BP37)=0,"",MEDIAN(BP8:BP37))</f>
-        <v/>
-      </c>
-      <c r="BQ39" s="82" t="str">
+      <c r="BN39" s="79" t="str">
+        <f t="shared" ref="BN39:BO39" si="76">IF(SUM(BN8:BN37)=0,"",MEDIAN(BN8:BN37))</f>
+        <v/>
+      </c>
+      <c r="BO39" s="80" t="str">
+        <f t="shared" si="76"/>
+        <v/>
+      </c>
+      <c r="BP39" s="80" t="str">
+        <f t="shared" ref="BP39" si="77">IF(SUM(BP8:BP37)=0,"",MEDIAN(BP8:BP37))</f>
+        <v/>
+      </c>
+      <c r="BQ39" s="78" t="str">
         <f>IF(SUM(BQ8:BQ37)=0,"",MEDIAN(BQ8:BQ37))</f>
         <v/>
       </c>
       <c r="BR39" s="79" t="str">
-        <f t="shared" ref="BR39:BS39" si="81">IF(SUM(BR8:BR37)=0,"",MEDIAN(BR8:BR37))</f>
+        <f t="shared" ref="BR39:BS39" si="78">IF(SUM(BR8:BR37)=0,"",MEDIAN(BR8:BR37))</f>
         <v/>
       </c>
       <c r="BS39" s="80" t="str">
-        <f t="shared" si="81"/>
-        <v/>
-      </c>
-      <c r="BT39" s="80" t="str">
-        <f t="shared" ref="BT39" si="82">IF(SUM(BT8:BT37)=0,"",MEDIAN(BT8:BT37))</f>
-        <v/>
-      </c>
-      <c r="BU39" s="78" t="str">
+        <f t="shared" si="78"/>
+        <v/>
+      </c>
+      <c r="BT39" s="81" t="str">
+        <f t="shared" ref="BT39" si="79">IF(SUM(BT8:BT37)=0,"",MEDIAN(BT8:BT37))</f>
+        <v/>
+      </c>
+      <c r="BU39" s="65" t="str">
         <f>IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
         <v/>
       </c>
-      <c r="BV39" s="79" t="str">
-        <f t="shared" ref="BV39:BW39" si="83">IF(SUM(BV8:BV37)=0,"",MEDIAN(BV8:BV37))</f>
-        <v/>
-      </c>
-      <c r="BW39" s="80" t="str">
-        <f t="shared" si="83"/>
-        <v/>
-      </c>
-      <c r="BX39" s="81" t="str">
-        <f t="shared" ref="BX39" si="84">IF(SUM(BX8:BX37)=0,"",MEDIAN(BX8:BX37))</f>
-        <v/>
-      </c>
-      <c r="BY39" s="65" t="str">
-        <f>IF(SUM(BY8:BY37)=0,"",MEDIAN(BY8:BY37))</f>
-        <v/>
-      </c>
-      <c r="BZ39" s="66" t="str">
-        <f t="shared" ref="BZ39:CA39" si="85">IF(SUM(BZ8:BZ37)=0,"",MEDIAN(BZ8:BZ37))</f>
-        <v/>
-      </c>
-      <c r="CA39" s="67" t="str">
-        <f t="shared" si="85"/>
-        <v/>
-      </c>
-      <c r="CB39" s="68" t="str">
-        <f t="shared" ref="CB39" si="86">IF(SUM(CB8:CB37)=0,"",MEDIAN(CB8:CB37))</f>
+      <c r="BV39" s="66" t="str">
+        <f t="shared" ref="BV39:BW39" si="80">IF(SUM(BV8:BV37)=0,"",MEDIAN(BV8:BV37))</f>
+        <v/>
+      </c>
+      <c r="BW39" s="67" t="str">
+        <f t="shared" si="80"/>
+        <v/>
+      </c>
+      <c r="BX39" s="68" t="str">
+        <f t="shared" ref="BX39" si="81">IF(SUM(BX8:BX37)=0,"",MEDIAN(BX8:BX37))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="114" t="s">
+    <row r="40" spans="1:76" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="115"/>
+      <c r="B40" s="114"/>
       <c r="C40" s="65" t="str">
         <f>IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
         <v/>
       </c>
       <c r="D40" s="66" t="str">
-        <f t="shared" ref="D40:E40" si="87">IF(SUM(D8:D37)=0,"",MAX(D8:D37))</f>
+        <f t="shared" ref="D40:E40" si="82">IF(SUM(D8:D37)=0,"",MAX(D8:D37))</f>
         <v/>
       </c>
       <c r="E40" s="67" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="82"/>
         <v/>
       </c>
       <c r="F40" s="68" t="str">
-        <f t="shared" ref="F40:AL40" si="88">IF(SUM(F8:F37)=0,"",MAX(F8:F37))</f>
+        <f t="shared" ref="F40:AL40" si="83">IF(SUM(F8:F37)=0,"",MAX(F8:F37))</f>
         <v/>
       </c>
       <c r="G40" s="65" t="str">
@@ -8367,15 +8080,15 @@
         <v/>
       </c>
       <c r="H40" s="66" t="str">
-        <f t="shared" ref="H40:I40" si="89">IF(SUM(H8:H37)=0,"",MAX(H8:H37))</f>
+        <f t="shared" ref="H40:I40" si="84">IF(SUM(H8:H37)=0,"",MAX(H8:H37))</f>
         <v/>
       </c>
       <c r="I40" s="67" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="84"/>
         <v/>
       </c>
       <c r="J40" s="68" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="K40" s="69" t="str">
@@ -8383,15 +8096,15 @@
         <v/>
       </c>
       <c r="L40" s="66" t="str">
-        <f t="shared" ref="L40:M40" si="90">IF(SUM(L8:L37)=0,"",MAX(L8:L37))</f>
+        <f t="shared" ref="L40:M40" si="85">IF(SUM(L8:L37)=0,"",MAX(L8:L37))</f>
         <v/>
       </c>
       <c r="M40" s="67" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="N40" s="67" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="O40" s="65" t="str">
@@ -8399,15 +8112,15 @@
         <v/>
       </c>
       <c r="P40" s="66" t="str">
-        <f t="shared" ref="P40:Q40" si="91">IF(SUM(P8:P37)=0,"",MAX(P8:P37))</f>
+        <f t="shared" ref="P40:Q40" si="86">IF(SUM(P8:P37)=0,"",MAX(P8:P37))</f>
         <v/>
       </c>
       <c r="Q40" s="67" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="R40" s="68" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="S40" s="65" t="str">
@@ -8415,15 +8128,15 @@
         <v/>
       </c>
       <c r="T40" s="66" t="str">
-        <f t="shared" ref="T40:U40" si="92">IF(SUM(T8:T37)=0,"",MAX(T8:T37))</f>
+        <f t="shared" ref="T40:U40" si="87">IF(SUM(T8:T37)=0,"",MAX(T8:T37))</f>
         <v/>
       </c>
       <c r="U40" s="67" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="V40" s="68" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="W40" s="69" t="str">
@@ -8431,15 +8144,15 @@
         <v/>
       </c>
       <c r="X40" s="66" t="str">
-        <f t="shared" ref="X40:Y40" si="93">IF(SUM(X8:X37)=0,"",MAX(X8:X37))</f>
+        <f t="shared" ref="X40:Y40" si="88">IF(SUM(X8:X37)=0,"",MAX(X8:X37))</f>
         <v/>
       </c>
       <c r="Y40" s="67" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="Z40" s="67" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="AA40" s="65" t="str">
@@ -8447,15 +8160,15 @@
         <v/>
       </c>
       <c r="AB40" s="66" t="str">
-        <f t="shared" ref="AB40:AC40" si="94">IF(SUM(AB8:AB37)=0,"",MAX(AB8:AB37))</f>
+        <f t="shared" ref="AB40:AC40" si="89">IF(SUM(AB8:AB37)=0,"",MAX(AB8:AB37))</f>
         <v/>
       </c>
       <c r="AC40" s="67" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="AD40" s="68" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="AE40" s="65" t="str">
@@ -8463,15 +8176,15 @@
         <v/>
       </c>
       <c r="AF40" s="66" t="str">
-        <f t="shared" ref="AF40:AG40" si="95">IF(SUM(AF8:AF37)=0,"",MAX(AF8:AF37))</f>
+        <f t="shared" ref="AF40:AG40" si="90">IF(SUM(AF8:AF37)=0,"",MAX(AF8:AF37))</f>
         <v/>
       </c>
       <c r="AG40" s="67" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="AH40" s="68" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="AI40" s="69" t="str">
@@ -8479,15 +8192,15 @@
         <v/>
       </c>
       <c r="AJ40" s="66" t="str">
-        <f t="shared" ref="AJ40:AK40" si="96">IF(SUM(AJ8:AJ37)=0,"",MAX(AJ8:AJ37))</f>
+        <f t="shared" ref="AJ40:AK40" si="91">IF(SUM(AJ8:AJ37)=0,"",MAX(AJ8:AJ37))</f>
         <v/>
       </c>
       <c r="AK40" s="67" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="AL40" s="67" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="AM40" s="74" t="str">
@@ -8495,67 +8208,67 @@
         <v/>
       </c>
       <c r="AN40" s="75" t="str">
-        <f t="shared" ref="AN40:AO40" si="97">IF(SUM(AN8:AN37)=0,"",MAX(AN8:AN37))</f>
+        <f t="shared" ref="AN40:AO40" si="92">IF(SUM(AN8:AN37)=0,"",MAX(AN8:AN37))</f>
         <v/>
       </c>
       <c r="AO40" s="76" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="AP40" s="77" t="str">
         <f>IF(SUM(AP8:AP37)=0,"",MAX(AP8:AP37))</f>
         <v/>
       </c>
-      <c r="AQ40" s="114" t="s">
+      <c r="AQ40" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="AR40" s="115"/>
+      <c r="AR40" s="114"/>
       <c r="AS40" s="78" t="str">
         <f>IF(SUM(AS8:AS37)=0,"",MAX(AS8:AS37))</f>
         <v/>
       </c>
       <c r="AT40" s="79" t="str">
-        <f t="shared" ref="AT40:AU40" si="98">IF(SUM(AT8:AT37)=0,"",MAX(AT8:AT37))</f>
+        <f t="shared" ref="AT40:AU40" si="93">IF(SUM(AT8:AT37)=0,"",MAX(AT8:AT37))</f>
         <v/>
       </c>
       <c r="AU40" s="80" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="AV40" s="81" t="str">
-        <f t="shared" ref="AV40" si="99">IF(SUM(AV8:AV37)=0,"",MAX(AV8:AV37))</f>
-        <v/>
-      </c>
-      <c r="AW40" s="78" t="str">
+        <f t="shared" ref="AV40" si="94">IF(SUM(AV8:AV37)=0,"",MAX(AV8:AV37))</f>
+        <v/>
+      </c>
+      <c r="AW40" s="82" t="str">
         <f>IF(SUM(AW8:AW37)=0,"",MAX(AW8:AW37))</f>
         <v/>
       </c>
       <c r="AX40" s="79" t="str">
-        <f t="shared" ref="AX40:AY40" si="100">IF(SUM(AX8:AX37)=0,"",MAX(AX8:AX37))</f>
+        <f t="shared" ref="AX40:AY40" si="95">IF(SUM(AX8:AX37)=0,"",MAX(AX8:AX37))</f>
         <v/>
       </c>
       <c r="AY40" s="80" t="str">
-        <f t="shared" si="100"/>
-        <v/>
-      </c>
-      <c r="AZ40" s="81" t="str">
-        <f t="shared" ref="AZ40" si="101">IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
-        <v/>
-      </c>
-      <c r="BA40" s="82" t="str">
+        <f t="shared" si="95"/>
+        <v/>
+      </c>
+      <c r="AZ40" s="80" t="str">
+        <f t="shared" ref="AZ40" si="96">IF(SUM(AZ8:AZ37)=0,"",MAX(AZ8:AZ37))</f>
+        <v/>
+      </c>
+      <c r="BA40" s="78" t="str">
         <f>IF(SUM(BA8:BA37)=0,"",MAX(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB40" s="79" t="str">
-        <f t="shared" ref="BB40:BC40" si="102">IF(SUM(BB8:BB37)=0,"",MAX(BB8:BB37))</f>
+        <f t="shared" ref="BB40:BC40" si="97">IF(SUM(BB8:BB37)=0,"",MAX(BB8:BB37))</f>
         <v/>
       </c>
       <c r="BC40" s="80" t="str">
-        <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="BD40" s="80" t="str">
-        <f t="shared" ref="BD40" si="103">IF(SUM(BD8:BD37)=0,"",MAX(BD8:BD37))</f>
+        <f t="shared" si="97"/>
+        <v/>
+      </c>
+      <c r="BD40" s="81" t="str">
+        <f t="shared" ref="BD40" si="98">IF(SUM(BD8:BD37)=0,"",MAX(BD8:BD37))</f>
         <v/>
       </c>
       <c r="BE40" s="78" t="str">
@@ -8563,117 +8276,101 @@
         <v/>
       </c>
       <c r="BF40" s="79" t="str">
-        <f t="shared" ref="BF40:BG40" si="104">IF(SUM(BF8:BF37)=0,"",MAX(BF8:BF37))</f>
+        <f t="shared" ref="BF40:BG40" si="99">IF(SUM(BF8:BF37)=0,"",MAX(BF8:BF37))</f>
         <v/>
       </c>
       <c r="BG40" s="80" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="BH40" s="81" t="str">
-        <f t="shared" ref="BH40" si="105">IF(SUM(BH8:BH37)=0,"",MAX(BH8:BH37))</f>
-        <v/>
-      </c>
-      <c r="BI40" s="78" t="str">
+        <f t="shared" ref="BH40" si="100">IF(SUM(BH8:BH37)=0,"",MAX(BH8:BH37))</f>
+        <v/>
+      </c>
+      <c r="BI40" s="65" t="str">
         <f>IF(SUM(BI8:BI37)=0,"",MAX(BI8:BI37))</f>
         <v/>
       </c>
-      <c r="BJ40" s="79" t="str">
-        <f t="shared" ref="BJ40:BK40" si="106">IF(SUM(BJ8:BJ37)=0,"",MAX(BJ8:BJ37))</f>
-        <v/>
-      </c>
-      <c r="BK40" s="80" t="str">
-        <f t="shared" si="106"/>
-        <v/>
-      </c>
-      <c r="BL40" s="81" t="str">
-        <f t="shared" ref="BL40" si="107">IF(SUM(BL8:BL37)=0,"",MAX(BL8:BL37))</f>
-        <v/>
-      </c>
-      <c r="BM40" s="65" t="str">
+      <c r="BJ40" s="66" t="str">
+        <f t="shared" ref="BJ40:BK40" si="101">IF(SUM(BJ8:BJ37)=0,"",MAX(BJ8:BJ37))</f>
+        <v/>
+      </c>
+      <c r="BK40" s="67" t="str">
+        <f t="shared" si="101"/>
+        <v/>
+      </c>
+      <c r="BL40" s="68" t="str">
+        <f t="shared" ref="BL40" si="102">IF(SUM(BL8:BL37)=0,"",MAX(BL8:BL37))</f>
+        <v/>
+      </c>
+      <c r="BM40" s="82" t="str">
         <f>IF(SUM(BM8:BM37)=0,"",MAX(BM8:BM37))</f>
         <v/>
       </c>
-      <c r="BN40" s="66" t="str">
-        <f t="shared" ref="BN40:BO40" si="108">IF(SUM(BN8:BN37)=0,"",MAX(BN8:BN37))</f>
-        <v/>
-      </c>
-      <c r="BO40" s="67" t="str">
-        <f t="shared" si="108"/>
-        <v/>
-      </c>
-      <c r="BP40" s="68" t="str">
-        <f t="shared" ref="BP40" si="109">IF(SUM(BP8:BP37)=0,"",MAX(BP8:BP37))</f>
-        <v/>
-      </c>
-      <c r="BQ40" s="82" t="str">
+      <c r="BN40" s="79" t="str">
+        <f t="shared" ref="BN40:BO40" si="103">IF(SUM(BN8:BN37)=0,"",MAX(BN8:BN37))</f>
+        <v/>
+      </c>
+      <c r="BO40" s="80" t="str">
+        <f t="shared" si="103"/>
+        <v/>
+      </c>
+      <c r="BP40" s="80" t="str">
+        <f t="shared" ref="BP40" si="104">IF(SUM(BP8:BP37)=0,"",MAX(BP8:BP37))</f>
+        <v/>
+      </c>
+      <c r="BQ40" s="78" t="str">
         <f>IF(SUM(BQ8:BQ37)=0,"",MAX(BQ8:BQ37))</f>
         <v/>
       </c>
       <c r="BR40" s="79" t="str">
-        <f t="shared" ref="BR40:BS40" si="110">IF(SUM(BR8:BR37)=0,"",MAX(BR8:BR37))</f>
+        <f t="shared" ref="BR40:BS40" si="105">IF(SUM(BR8:BR37)=0,"",MAX(BR8:BR37))</f>
         <v/>
       </c>
       <c r="BS40" s="80" t="str">
-        <f t="shared" si="110"/>
-        <v/>
-      </c>
-      <c r="BT40" s="80" t="str">
-        <f t="shared" ref="BT40" si="111">IF(SUM(BT8:BT37)=0,"",MAX(BT8:BT37))</f>
-        <v/>
-      </c>
-      <c r="BU40" s="78" t="str">
+        <f t="shared" si="105"/>
+        <v/>
+      </c>
+      <c r="BT40" s="81" t="str">
+        <f t="shared" ref="BT40" si="106">IF(SUM(BT8:BT37)=0,"",MAX(BT8:BT37))</f>
+        <v/>
+      </c>
+      <c r="BU40" s="65" t="str">
         <f>IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
         <v/>
       </c>
-      <c r="BV40" s="79" t="str">
-        <f t="shared" ref="BV40:BW40" si="112">IF(SUM(BV8:BV37)=0,"",MAX(BV8:BV37))</f>
-        <v/>
-      </c>
-      <c r="BW40" s="80" t="str">
-        <f t="shared" si="112"/>
-        <v/>
-      </c>
-      <c r="BX40" s="81" t="str">
-        <f t="shared" ref="BX40" si="113">IF(SUM(BX8:BX37)=0,"",MAX(BX8:BX37))</f>
-        <v/>
-      </c>
-      <c r="BY40" s="65" t="str">
-        <f>IF(SUM(BY8:BY37)=0,"",MAX(BY8:BY37))</f>
-        <v/>
-      </c>
-      <c r="BZ40" s="66" t="str">
-        <f t="shared" ref="BZ40:CA40" si="114">IF(SUM(BZ8:BZ37)=0,"",MAX(BZ8:BZ37))</f>
-        <v/>
-      </c>
-      <c r="CA40" s="67" t="str">
-        <f t="shared" si="114"/>
-        <v/>
-      </c>
-      <c r="CB40" s="68" t="str">
-        <f t="shared" ref="CB40" si="115">IF(SUM(CB8:CB37)=0,"",MAX(CB8:CB37))</f>
+      <c r="BV40" s="66" t="str">
+        <f t="shared" ref="BV40:BW40" si="107">IF(SUM(BV8:BV37)=0,"",MAX(BV8:BV37))</f>
+        <v/>
+      </c>
+      <c r="BW40" s="67" t="str">
+        <f t="shared" si="107"/>
+        <v/>
+      </c>
+      <c r="BX40" s="68" t="str">
+        <f t="shared" ref="BX40" si="108">IF(SUM(BX8:BX37)=0,"",MAX(BX8:BX37))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="114" t="s">
+    <row r="41" spans="1:76" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="115"/>
+      <c r="B41" s="114"/>
       <c r="C41" s="65" t="str">
         <f>IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
         <v/>
       </c>
       <c r="D41" s="66" t="str">
-        <f t="shared" ref="D41:E41" si="116">IF(SUM(D8:D37)=0,"",MIN(D8:D37))</f>
+        <f t="shared" ref="D41:E41" si="109">IF(SUM(D8:D37)=0,"",MIN(D8:D37))</f>
         <v/>
       </c>
       <c r="E41" s="67" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="F41" s="68" t="str">
-        <f t="shared" ref="F41:AP41" si="117">IF(SUM(F8:F37)=0,"",MIN(F8:F37))</f>
+        <f t="shared" ref="F41:AP41" si="110">IF(SUM(F8:F37)=0,"",MIN(F8:F37))</f>
         <v/>
       </c>
       <c r="G41" s="65" t="str">
@@ -8681,15 +8378,15 @@
         <v/>
       </c>
       <c r="H41" s="66" t="str">
-        <f t="shared" ref="H41:I41" si="118">IF(SUM(H8:H37)=0,"",MIN(H8:H37))</f>
+        <f t="shared" ref="H41:I41" si="111">IF(SUM(H8:H37)=0,"",MIN(H8:H37))</f>
         <v/>
       </c>
       <c r="I41" s="67" t="str">
-        <f t="shared" si="118"/>
+        <f t="shared" si="111"/>
         <v/>
       </c>
       <c r="J41" s="68" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="K41" s="69" t="str">
@@ -8697,15 +8394,15 @@
         <v/>
       </c>
       <c r="L41" s="66" t="str">
-        <f t="shared" ref="L41:M41" si="119">IF(SUM(L8:L37)=0,"",MIN(L8:L37))</f>
+        <f t="shared" ref="L41:M41" si="112">IF(SUM(L8:L37)=0,"",MIN(L8:L37))</f>
         <v/>
       </c>
       <c r="M41" s="67" t="str">
-        <f t="shared" si="119"/>
+        <f t="shared" si="112"/>
         <v/>
       </c>
       <c r="N41" s="67" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="O41" s="65" t="str">
@@ -8713,15 +8410,15 @@
         <v/>
       </c>
       <c r="P41" s="66" t="str">
-        <f t="shared" ref="P41:Q41" si="120">IF(SUM(P8:P37)=0,"",MIN(P8:P37))</f>
+        <f t="shared" ref="P41:Q41" si="113">IF(SUM(P8:P37)=0,"",MIN(P8:P37))</f>
         <v/>
       </c>
       <c r="Q41" s="67" t="str">
-        <f t="shared" si="120"/>
+        <f t="shared" si="113"/>
         <v/>
       </c>
       <c r="R41" s="68" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="S41" s="65" t="str">
@@ -8729,15 +8426,15 @@
         <v/>
       </c>
       <c r="T41" s="66" t="str">
-        <f t="shared" ref="T41:U41" si="121">IF(SUM(T8:T37)=0,"",MIN(T8:T37))</f>
+        <f t="shared" ref="T41:U41" si="114">IF(SUM(T8:T37)=0,"",MIN(T8:T37))</f>
         <v/>
       </c>
       <c r="U41" s="67" t="str">
-        <f t="shared" si="121"/>
+        <f t="shared" si="114"/>
         <v/>
       </c>
       <c r="V41" s="68" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="W41" s="69" t="str">
@@ -8745,15 +8442,15 @@
         <v/>
       </c>
       <c r="X41" s="66" t="str">
-        <f t="shared" ref="X41:Y41" si="122">IF(SUM(X8:X37)=0,"",MIN(X8:X37))</f>
+        <f t="shared" ref="X41:Y41" si="115">IF(SUM(X8:X37)=0,"",MIN(X8:X37))</f>
         <v/>
       </c>
       <c r="Y41" s="67" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="115"/>
         <v/>
       </c>
       <c r="Z41" s="67" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="AA41" s="65" t="str">
@@ -8761,15 +8458,15 @@
         <v/>
       </c>
       <c r="AB41" s="66" t="str">
-        <f t="shared" ref="AB41:AC41" si="123">IF(SUM(AB8:AB37)=0,"",MIN(AB8:AB37))</f>
+        <f t="shared" ref="AB41:AC41" si="116">IF(SUM(AB8:AB37)=0,"",MIN(AB8:AB37))</f>
         <v/>
       </c>
       <c r="AC41" s="67" t="str">
-        <f t="shared" si="123"/>
+        <f t="shared" si="116"/>
         <v/>
       </c>
       <c r="AD41" s="68" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="AE41" s="65" t="str">
@@ -8777,15 +8474,15 @@
         <v/>
       </c>
       <c r="AF41" s="66" t="str">
-        <f t="shared" ref="AF41:AG41" si="124">IF(SUM(AF8:AF37)=0,"",MIN(AF8:AF37))</f>
+        <f t="shared" ref="AF41:AG41" si="117">IF(SUM(AF8:AF37)=0,"",MIN(AF8:AF37))</f>
         <v/>
       </c>
       <c r="AG41" s="67" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="AH41" s="68" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="AI41" s="69" t="str">
@@ -8793,15 +8490,15 @@
         <v/>
       </c>
       <c r="AJ41" s="66" t="str">
-        <f t="shared" ref="AJ41:AK41" si="125">IF(SUM(AJ8:AJ37)=0,"",MIN(AJ8:AJ37))</f>
+        <f t="shared" ref="AJ41:AK41" si="118">IF(SUM(AJ8:AJ37)=0,"",MIN(AJ8:AJ37))</f>
         <v/>
       </c>
       <c r="AK41" s="67" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="118"/>
         <v/>
       </c>
       <c r="AL41" s="67" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="AM41" s="74" t="str">
@@ -8809,67 +8506,67 @@
         <v/>
       </c>
       <c r="AN41" s="75" t="str">
-        <f t="shared" ref="AN41:AO41" si="126">IF(SUM(AN8:AN37)=0,"",MIN(AN8:AN37))</f>
+        <f t="shared" ref="AN41:AO41" si="119">IF(SUM(AN8:AN37)=0,"",MIN(AN8:AN37))</f>
         <v/>
       </c>
       <c r="AO41" s="76" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" si="119"/>
         <v/>
       </c>
       <c r="AP41" s="77" t="str">
-        <f t="shared" si="117"/>
-        <v/>
-      </c>
-      <c r="AQ41" s="114" t="s">
+        <f t="shared" si="110"/>
+        <v/>
+      </c>
+      <c r="AQ41" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="AR41" s="115"/>
+      <c r="AR41" s="114"/>
       <c r="AS41" s="78" t="str">
         <f>IF(SUM(AS8:AS37)=0,"",MIN(AS8:AS37))</f>
         <v/>
       </c>
       <c r="AT41" s="79" t="str">
-        <f t="shared" ref="AT41:AU41" si="127">IF(SUM(AT8:AT37)=0,"",MIN(AT8:AT37))</f>
+        <f t="shared" ref="AT41:AU41" si="120">IF(SUM(AT8:AT37)=0,"",MIN(AT8:AT37))</f>
         <v/>
       </c>
       <c r="AU41" s="80" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="120"/>
         <v/>
       </c>
       <c r="AV41" s="81" t="str">
-        <f t="shared" ref="AV41" si="128">IF(SUM(AV8:AV37)=0,"",MIN(AV8:AV37))</f>
-        <v/>
-      </c>
-      <c r="AW41" s="78" t="str">
+        <f t="shared" ref="AV41" si="121">IF(SUM(AV8:AV37)=0,"",MIN(AV8:AV37))</f>
+        <v/>
+      </c>
+      <c r="AW41" s="82" t="str">
         <f>IF(SUM(AW8:AW37)=0,"",MIN(AW8:AW37))</f>
         <v/>
       </c>
       <c r="AX41" s="79" t="str">
-        <f t="shared" ref="AX41:AY41" si="129">IF(SUM(AX8:AX37)=0,"",MIN(AX8:AX37))</f>
+        <f t="shared" ref="AX41:AY41" si="122">IF(SUM(AX8:AX37)=0,"",MIN(AX8:AX37))</f>
         <v/>
       </c>
       <c r="AY41" s="80" t="str">
-        <f t="shared" si="129"/>
-        <v/>
-      </c>
-      <c r="AZ41" s="81" t="str">
-        <f t="shared" ref="AZ41" si="130">IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
-        <v/>
-      </c>
-      <c r="BA41" s="82" t="str">
+        <f t="shared" si="122"/>
+        <v/>
+      </c>
+      <c r="AZ41" s="80" t="str">
+        <f t="shared" ref="AZ41" si="123">IF(SUM(AZ8:AZ37)=0,"",MIN(AZ8:AZ37))</f>
+        <v/>
+      </c>
+      <c r="BA41" s="78" t="str">
         <f>IF(SUM(BA8:BA37)=0,"",MIN(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB41" s="79" t="str">
-        <f t="shared" ref="BB41:BC41" si="131">IF(SUM(BB8:BB37)=0,"",MIN(BB8:BB37))</f>
+        <f t="shared" ref="BB41:BC41" si="124">IF(SUM(BB8:BB37)=0,"",MIN(BB8:BB37))</f>
         <v/>
       </c>
       <c r="BC41" s="80" t="str">
-        <f t="shared" si="131"/>
-        <v/>
-      </c>
-      <c r="BD41" s="80" t="str">
-        <f t="shared" ref="BD41" si="132">IF(SUM(BD8:BD37)=0,"",MIN(BD8:BD37))</f>
+        <f t="shared" si="124"/>
+        <v/>
+      </c>
+      <c r="BD41" s="81" t="str">
+        <f t="shared" ref="BD41" si="125">IF(SUM(BD8:BD37)=0,"",MIN(BD8:BD37))</f>
         <v/>
       </c>
       <c r="BE41" s="78" t="str">
@@ -8877,117 +8574,101 @@
         <v/>
       </c>
       <c r="BF41" s="79" t="str">
-        <f t="shared" ref="BF41:BG41" si="133">IF(SUM(BF8:BF37)=0,"",MIN(BF8:BF37))</f>
+        <f t="shared" ref="BF41:BG41" si="126">IF(SUM(BF8:BF37)=0,"",MIN(BF8:BF37))</f>
         <v/>
       </c>
       <c r="BG41" s="80" t="str">
-        <f t="shared" si="133"/>
+        <f t="shared" si="126"/>
         <v/>
       </c>
       <c r="BH41" s="81" t="str">
-        <f t="shared" ref="BH41" si="134">IF(SUM(BH8:BH37)=0,"",MIN(BH8:BH37))</f>
-        <v/>
-      </c>
-      <c r="BI41" s="78" t="str">
+        <f t="shared" ref="BH41" si="127">IF(SUM(BH8:BH37)=0,"",MIN(BH8:BH37))</f>
+        <v/>
+      </c>
+      <c r="BI41" s="65" t="str">
         <f>IF(SUM(BI8:BI37)=0,"",MIN(BI8:BI37))</f>
         <v/>
       </c>
-      <c r="BJ41" s="79" t="str">
-        <f t="shared" ref="BJ41:BK41" si="135">IF(SUM(BJ8:BJ37)=0,"",MIN(BJ8:BJ37))</f>
-        <v/>
-      </c>
-      <c r="BK41" s="80" t="str">
-        <f t="shared" si="135"/>
-        <v/>
-      </c>
-      <c r="BL41" s="81" t="str">
-        <f t="shared" ref="BL41" si="136">IF(SUM(BL8:BL37)=0,"",MIN(BL8:BL37))</f>
-        <v/>
-      </c>
-      <c r="BM41" s="65" t="str">
+      <c r="BJ41" s="66" t="str">
+        <f t="shared" ref="BJ41:BK41" si="128">IF(SUM(BJ8:BJ37)=0,"",MIN(BJ8:BJ37))</f>
+        <v/>
+      </c>
+      <c r="BK41" s="67" t="str">
+        <f t="shared" si="128"/>
+        <v/>
+      </c>
+      <c r="BL41" s="68" t="str">
+        <f t="shared" ref="BL41" si="129">IF(SUM(BL8:BL37)=0,"",MIN(BL8:BL37))</f>
+        <v/>
+      </c>
+      <c r="BM41" s="82" t="str">
         <f>IF(SUM(BM8:BM37)=0,"",MIN(BM8:BM37))</f>
         <v/>
       </c>
-      <c r="BN41" s="66" t="str">
-        <f t="shared" ref="BN41:BO41" si="137">IF(SUM(BN8:BN37)=0,"",MIN(BN8:BN37))</f>
-        <v/>
-      </c>
-      <c r="BO41" s="67" t="str">
-        <f t="shared" si="137"/>
-        <v/>
-      </c>
-      <c r="BP41" s="68" t="str">
-        <f t="shared" ref="BP41" si="138">IF(SUM(BP8:BP37)=0,"",MIN(BP8:BP37))</f>
-        <v/>
-      </c>
-      <c r="BQ41" s="82" t="str">
+      <c r="BN41" s="79" t="str">
+        <f t="shared" ref="BN41:BO41" si="130">IF(SUM(BN8:BN37)=0,"",MIN(BN8:BN37))</f>
+        <v/>
+      </c>
+      <c r="BO41" s="80" t="str">
+        <f t="shared" si="130"/>
+        <v/>
+      </c>
+      <c r="BP41" s="80" t="str">
+        <f t="shared" ref="BP41" si="131">IF(SUM(BP8:BP37)=0,"",MIN(BP8:BP37))</f>
+        <v/>
+      </c>
+      <c r="BQ41" s="78" t="str">
         <f>IF(SUM(BQ8:BQ37)=0,"",MIN(BQ8:BQ37))</f>
         <v/>
       </c>
       <c r="BR41" s="79" t="str">
-        <f t="shared" ref="BR41:BS41" si="139">IF(SUM(BR8:BR37)=0,"",MIN(BR8:BR37))</f>
+        <f t="shared" ref="BR41:BS41" si="132">IF(SUM(BR8:BR37)=0,"",MIN(BR8:BR37))</f>
         <v/>
       </c>
       <c r="BS41" s="80" t="str">
-        <f t="shared" si="139"/>
-        <v/>
-      </c>
-      <c r="BT41" s="80" t="str">
-        <f t="shared" ref="BT41" si="140">IF(SUM(BT8:BT37)=0,"",MIN(BT8:BT37))</f>
-        <v/>
-      </c>
-      <c r="BU41" s="78" t="str">
+        <f t="shared" si="132"/>
+        <v/>
+      </c>
+      <c r="BT41" s="81" t="str">
+        <f t="shared" ref="BT41" si="133">IF(SUM(BT8:BT37)=0,"",MIN(BT8:BT37))</f>
+        <v/>
+      </c>
+      <c r="BU41" s="65" t="str">
         <f>IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
         <v/>
       </c>
-      <c r="BV41" s="79" t="str">
-        <f t="shared" ref="BV41:BW41" si="141">IF(SUM(BV8:BV37)=0,"",MIN(BV8:BV37))</f>
-        <v/>
-      </c>
-      <c r="BW41" s="80" t="str">
-        <f t="shared" si="141"/>
-        <v/>
-      </c>
-      <c r="BX41" s="81" t="str">
-        <f t="shared" ref="BX41" si="142">IF(SUM(BX8:BX37)=0,"",MIN(BX8:BX37))</f>
-        <v/>
-      </c>
-      <c r="BY41" s="65" t="str">
-        <f>IF(SUM(BY8:BY37)=0,"",MIN(BY8:BY37))</f>
-        <v/>
-      </c>
-      <c r="BZ41" s="66" t="str">
-        <f t="shared" ref="BZ41:CA41" si="143">IF(SUM(BZ8:BZ37)=0,"",MIN(BZ8:BZ37))</f>
-        <v/>
-      </c>
-      <c r="CA41" s="67" t="str">
-        <f t="shared" si="143"/>
-        <v/>
-      </c>
-      <c r="CB41" s="68" t="str">
-        <f t="shared" ref="CB41" si="144">IF(SUM(CB8:CB37)=0,"",MIN(CB8:CB37))</f>
+      <c r="BV41" s="66" t="str">
+        <f t="shared" ref="BV41:BW41" si="134">IF(SUM(BV8:BV37)=0,"",MIN(BV8:BV37))</f>
+        <v/>
+      </c>
+      <c r="BW41" s="67" t="str">
+        <f t="shared" si="134"/>
+        <v/>
+      </c>
+      <c r="BX41" s="68" t="str">
+        <f t="shared" ref="BX41" si="135">IF(SUM(BX8:BX37)=0,"",MIN(BX8:BX37))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="125" t="s">
+    <row r="42" spans="1:76" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="B42" s="126"/>
+      <c r="B42" s="117"/>
       <c r="C42" s="83" t="str">
         <f>IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
         <v/>
       </c>
       <c r="D42" s="84" t="str">
-        <f t="shared" ref="D42:E42" si="145">IF(D38="","",COUNTIF(D8:D37,"&lt;51")/COUNT(D8:D37)*100)</f>
+        <f t="shared" ref="D42:E42" si="136">IF(D38="","",COUNTIF(D8:D37,"&lt;51")/COUNT(D8:D37)*100)</f>
         <v/>
       </c>
       <c r="E42" s="85" t="str">
-        <f t="shared" si="145"/>
+        <f t="shared" si="136"/>
         <v/>
       </c>
       <c r="F42" s="86" t="str">
-        <f t="shared" ref="F42:AP42" si="146">IF(F38="","",COUNTIF(F8:F37,"&lt;51")/COUNT(F8:F37)*100)</f>
+        <f t="shared" ref="F42:AP42" si="137">IF(F38="","",COUNTIF(F8:F37,"&lt;51")/COUNT(F8:F37)*100)</f>
         <v/>
       </c>
       <c r="G42" s="83" t="str">
@@ -8995,15 +8676,15 @@
         <v/>
       </c>
       <c r="H42" s="84" t="str">
-        <f t="shared" ref="H42:I42" si="147">IF(H38="","",COUNTIF(H8:H37,"&lt;51")/COUNT(H8:H37)*100)</f>
+        <f t="shared" ref="H42:I42" si="138">IF(H38="","",COUNTIF(H8:H37,"&lt;51")/COUNT(H8:H37)*100)</f>
         <v/>
       </c>
       <c r="I42" s="85" t="str">
-        <f t="shared" si="147"/>
+        <f t="shared" si="138"/>
         <v/>
       </c>
       <c r="J42" s="86" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="K42" s="87" t="str">
@@ -9011,15 +8692,15 @@
         <v/>
       </c>
       <c r="L42" s="84" t="str">
-        <f t="shared" ref="L42:M42" si="148">IF(L38="","",COUNTIF(L8:L37,"&lt;51")/COUNT(L8:L37)*100)</f>
+        <f t="shared" ref="L42:M42" si="139">IF(L38="","",COUNTIF(L8:L37,"&lt;51")/COUNT(L8:L37)*100)</f>
         <v/>
       </c>
       <c r="M42" s="85" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v/>
       </c>
       <c r="N42" s="85" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="O42" s="83" t="str">
@@ -9027,15 +8708,15 @@
         <v/>
       </c>
       <c r="P42" s="84" t="str">
-        <f t="shared" ref="P42:Q42" si="149">IF(P38="","",COUNTIF(P8:P37,"&lt;51")/COUNT(P8:P37)*100)</f>
+        <f t="shared" ref="P42:Q42" si="140">IF(P38="","",COUNTIF(P8:P37,"&lt;51")/COUNT(P8:P37)*100)</f>
         <v/>
       </c>
       <c r="Q42" s="85" t="str">
-        <f t="shared" si="149"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="R42" s="86" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="S42" s="83" t="str">
@@ -9043,15 +8724,15 @@
         <v/>
       </c>
       <c r="T42" s="84" t="str">
-        <f t="shared" ref="T42:U42" si="150">IF(T38="","",COUNTIF(T8:T37,"&lt;51")/COUNT(T8:T37)*100)</f>
+        <f t="shared" ref="T42:U42" si="141">IF(T38="","",COUNTIF(T8:T37,"&lt;51")/COUNT(T8:T37)*100)</f>
         <v/>
       </c>
       <c r="U42" s="85" t="str">
-        <f t="shared" si="150"/>
+        <f t="shared" si="141"/>
         <v/>
       </c>
       <c r="V42" s="86" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="W42" s="87" t="str">
@@ -9059,15 +8740,15 @@
         <v/>
       </c>
       <c r="X42" s="84" t="str">
-        <f t="shared" ref="X42:Y42" si="151">IF(X38="","",COUNTIF(X8:X37,"&lt;51")/COUNT(X8:X37)*100)</f>
+        <f t="shared" ref="X42:Y42" si="142">IF(X38="","",COUNTIF(X8:X37,"&lt;51")/COUNT(X8:X37)*100)</f>
         <v/>
       </c>
       <c r="Y42" s="85" t="str">
-        <f t="shared" si="151"/>
+        <f t="shared" si="142"/>
         <v/>
       </c>
       <c r="Z42" s="85" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="AA42" s="83" t="str">
@@ -9075,15 +8756,15 @@
         <v/>
       </c>
       <c r="AB42" s="84" t="str">
-        <f t="shared" ref="AB42:AC42" si="152">IF(AB38="","",COUNTIF(AB8:AB37,"&lt;51")/COUNT(AB8:AB37)*100)</f>
+        <f t="shared" ref="AB42:AC42" si="143">IF(AB38="","",COUNTIF(AB8:AB37,"&lt;51")/COUNT(AB8:AB37)*100)</f>
         <v/>
       </c>
       <c r="AC42" s="85" t="str">
-        <f t="shared" si="152"/>
+        <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="AD42" s="86" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="AE42" s="83" t="str">
@@ -9091,15 +8772,15 @@
         <v/>
       </c>
       <c r="AF42" s="84" t="str">
-        <f t="shared" ref="AF42:AG42" si="153">IF(AF38="","",COUNTIF(AF8:AF37,"&lt;51")/COUNT(AF8:AF37)*100)</f>
+        <f t="shared" ref="AF42:AG42" si="144">IF(AF38="","",COUNTIF(AF8:AF37,"&lt;51")/COUNT(AF8:AF37)*100)</f>
         <v/>
       </c>
       <c r="AG42" s="85" t="str">
-        <f t="shared" si="153"/>
+        <f t="shared" si="144"/>
         <v/>
       </c>
       <c r="AH42" s="86" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="AI42" s="87" t="str">
@@ -9107,15 +8788,15 @@
         <v/>
       </c>
       <c r="AJ42" s="84" t="str">
-        <f t="shared" ref="AJ42:AK42" si="154">IF(AJ38="","",COUNTIF(AJ8:AJ37,"&lt;51")/COUNT(AJ8:AJ37)*100)</f>
+        <f t="shared" ref="AJ42:AK42" si="145">IF(AJ38="","",COUNTIF(AJ8:AJ37,"&lt;51")/COUNT(AJ8:AJ37)*100)</f>
         <v/>
       </c>
       <c r="AK42" s="85" t="str">
-        <f t="shared" si="154"/>
+        <f t="shared" si="145"/>
         <v/>
       </c>
       <c r="AL42" s="85" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="AM42" s="88" t="str">
@@ -9123,67 +8804,67 @@
         <v/>
       </c>
       <c r="AN42" s="89" t="str">
-        <f t="shared" ref="AN42:AO42" si="155">IF(AN38="","",COUNTIF(AN8:AN37,"&lt;51")/COUNT(AN8:AN37)*100)</f>
+        <f t="shared" ref="AN42:AO42" si="146">IF(AN38="","",COUNTIF(AN8:AN37,"&lt;51")/COUNT(AN8:AN37)*100)</f>
         <v/>
       </c>
       <c r="AO42" s="90" t="str">
-        <f t="shared" si="155"/>
+        <f t="shared" si="146"/>
         <v/>
       </c>
       <c r="AP42" s="91" t="str">
-        <f t="shared" si="146"/>
-        <v/>
-      </c>
-      <c r="AQ42" s="125" t="s">
+        <f t="shared" si="137"/>
+        <v/>
+      </c>
+      <c r="AQ42" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="AR42" s="126"/>
+      <c r="AR42" s="117"/>
       <c r="AS42" s="92" t="str">
         <f>IF(AS38="","",COUNTIF(AS8:AS37,"&lt;51")/COUNT(AS8:AS37)*100)</f>
         <v/>
       </c>
       <c r="AT42" s="93" t="str">
-        <f t="shared" ref="AT42:AU42" si="156">IF(AT38="","",COUNTIF(AT8:AT37,"&lt;51")/COUNT(AT8:AT37)*100)</f>
+        <f t="shared" ref="AT42:AU42" si="147">IF(AT38="","",COUNTIF(AT8:AT37,"&lt;51")/COUNT(AT8:AT37)*100)</f>
         <v/>
       </c>
       <c r="AU42" s="94" t="str">
-        <f t="shared" si="156"/>
+        <f t="shared" si="147"/>
         <v/>
       </c>
       <c r="AV42" s="95" t="str">
-        <f t="shared" ref="AV42" si="157">IF(AV38="","",COUNTIF(AV8:AV37,"&lt;51")/COUNT(AV8:AV37)*100)</f>
-        <v/>
-      </c>
-      <c r="AW42" s="92" t="str">
+        <f t="shared" ref="AV42" si="148">IF(AV38="","",COUNTIF(AV8:AV37,"&lt;51")/COUNT(AV8:AV37)*100)</f>
+        <v/>
+      </c>
+      <c r="AW42" s="96" t="str">
         <f>IF(AW38="","",COUNTIF(AW8:AW37,"&lt;51")/COUNT(AW8:AW37)*100)</f>
         <v/>
       </c>
       <c r="AX42" s="93" t="str">
-        <f t="shared" ref="AX42:AY42" si="158">IF(AX38="","",COUNTIF(AX8:AX37,"&lt;51")/COUNT(AX8:AX37)*100)</f>
+        <f t="shared" ref="AX42:AY42" si="149">IF(AX38="","",COUNTIF(AX8:AX37,"&lt;51")/COUNT(AX8:AX37)*100)</f>
         <v/>
       </c>
       <c r="AY42" s="94" t="str">
-        <f t="shared" si="158"/>
-        <v/>
-      </c>
-      <c r="AZ42" s="95" t="str">
-        <f t="shared" ref="AZ42" si="159">IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
-        <v/>
-      </c>
-      <c r="BA42" s="96" t="str">
+        <f t="shared" si="149"/>
+        <v/>
+      </c>
+      <c r="AZ42" s="94" t="str">
+        <f t="shared" ref="AZ42" si="150">IF(AZ38="","",COUNTIF(AZ8:AZ37,"&lt;51")/COUNT(AZ8:AZ37)*100)</f>
+        <v/>
+      </c>
+      <c r="BA42" s="92" t="str">
         <f>IF(BA38="","",COUNTIF(BA8:BA37,"&lt;51")/COUNT(BA8:BA37)*100)</f>
         <v/>
       </c>
       <c r="BB42" s="93" t="str">
-        <f t="shared" ref="BB42:BC42" si="160">IF(BB38="","",COUNTIF(BB8:BB37,"&lt;51")/COUNT(BB8:BB37)*100)</f>
+        <f t="shared" ref="BB42:BC42" si="151">IF(BB38="","",COUNTIF(BB8:BB37,"&lt;51")/COUNT(BB8:BB37)*100)</f>
         <v/>
       </c>
       <c r="BC42" s="94" t="str">
-        <f t="shared" si="160"/>
-        <v/>
-      </c>
-      <c r="BD42" s="94" t="str">
-        <f t="shared" ref="BD42" si="161">IF(BD38="","",COUNTIF(BD8:BD37,"&lt;51")/COUNT(BD8:BD37)*100)</f>
+        <f t="shared" si="151"/>
+        <v/>
+      </c>
+      <c r="BD42" s="95" t="str">
+        <f t="shared" ref="BD42" si="152">IF(BD38="","",COUNTIF(BD8:BD37,"&lt;51")/COUNT(BD8:BD37)*100)</f>
         <v/>
       </c>
       <c r="BE42" s="92" t="str">
@@ -9191,290 +8872,270 @@
         <v/>
       </c>
       <c r="BF42" s="93" t="str">
-        <f t="shared" ref="BF42:BG42" si="162">IF(BF38="","",COUNTIF(BF8:BF37,"&lt;51")/COUNT(BF8:BF37)*100)</f>
+        <f t="shared" ref="BF42:BG42" si="153">IF(BF38="","",COUNTIF(BF8:BF37,"&lt;51")/COUNT(BF8:BF37)*100)</f>
         <v/>
       </c>
       <c r="BG42" s="94" t="str">
-        <f t="shared" si="162"/>
+        <f t="shared" si="153"/>
         <v/>
       </c>
       <c r="BH42" s="95" t="str">
-        <f t="shared" ref="BH42" si="163">IF(BH38="","",COUNTIF(BH8:BH37,"&lt;51")/COUNT(BH8:BH37)*100)</f>
-        <v/>
-      </c>
-      <c r="BI42" s="92" t="str">
+        <f t="shared" ref="BH42" si="154">IF(BH38="","",COUNTIF(BH8:BH37,"&lt;51")/COUNT(BH8:BH37)*100)</f>
+        <v/>
+      </c>
+      <c r="BI42" s="83" t="str">
         <f>IF(BI38="","",COUNTIF(BI8:BI37,"&lt;51")/COUNT(BI8:BI37)*100)</f>
         <v/>
       </c>
-      <c r="BJ42" s="93" t="str">
-        <f t="shared" ref="BJ42:BK42" si="164">IF(BJ38="","",COUNTIF(BJ8:BJ37,"&lt;51")/COUNT(BJ8:BJ37)*100)</f>
-        <v/>
-      </c>
-      <c r="BK42" s="94" t="str">
-        <f t="shared" si="164"/>
-        <v/>
-      </c>
-      <c r="BL42" s="95" t="str">
-        <f t="shared" ref="BL42" si="165">IF(BL38="","",COUNTIF(BL8:BL37,"&lt;51")/COUNT(BL8:BL37)*100)</f>
-        <v/>
-      </c>
-      <c r="BM42" s="83" t="str">
+      <c r="BJ42" s="84" t="str">
+        <f t="shared" ref="BJ42:BK42" si="155">IF(BJ38="","",COUNTIF(BJ8:BJ37,"&lt;51")/COUNT(BJ8:BJ37)*100)</f>
+        <v/>
+      </c>
+      <c r="BK42" s="85" t="str">
+        <f t="shared" si="155"/>
+        <v/>
+      </c>
+      <c r="BL42" s="86" t="str">
+        <f t="shared" ref="BL42" si="156">IF(BL38="","",COUNTIF(BL8:BL37,"&lt;51")/COUNT(BL8:BL37)*100)</f>
+        <v/>
+      </c>
+      <c r="BM42" s="96" t="str">
         <f>IF(BM38="","",COUNTIF(BM8:BM37,"&lt;51")/COUNT(BM8:BM37)*100)</f>
         <v/>
       </c>
-      <c r="BN42" s="84" t="str">
-        <f t="shared" ref="BN42:BO42" si="166">IF(BN38="","",COUNTIF(BN8:BN37,"&lt;51")/COUNT(BN8:BN37)*100)</f>
-        <v/>
-      </c>
-      <c r="BO42" s="85" t="str">
-        <f t="shared" si="166"/>
-        <v/>
-      </c>
-      <c r="BP42" s="86" t="str">
-        <f t="shared" ref="BP42" si="167">IF(BP38="","",COUNTIF(BP8:BP37,"&lt;51")/COUNT(BP8:BP37)*100)</f>
-        <v/>
-      </c>
-      <c r="BQ42" s="96" t="str">
+      <c r="BN42" s="93" t="str">
+        <f t="shared" ref="BN42:BO42" si="157">IF(BN38="","",COUNTIF(BN8:BN37,"&lt;51")/COUNT(BN8:BN37)*100)</f>
+        <v/>
+      </c>
+      <c r="BO42" s="94" t="str">
+        <f t="shared" si="157"/>
+        <v/>
+      </c>
+      <c r="BP42" s="94" t="str">
+        <f t="shared" ref="BP42" si="158">IF(BP38="","",COUNTIF(BP8:BP37,"&lt;51")/COUNT(BP8:BP37)*100)</f>
+        <v/>
+      </c>
+      <c r="BQ42" s="92" t="str">
         <f>IF(BQ38="","",COUNTIF(BQ8:BQ37,"&lt;51")/COUNT(BQ8:BQ37)*100)</f>
         <v/>
       </c>
       <c r="BR42" s="93" t="str">
-        <f t="shared" ref="BR42:BS42" si="168">IF(BR38="","",COUNTIF(BR8:BR37,"&lt;51")/COUNT(BR8:BR37)*100)</f>
+        <f t="shared" ref="BR42:BS42" si="159">IF(BR38="","",COUNTIF(BR8:BR37,"&lt;51")/COUNT(BR8:BR37)*100)</f>
         <v/>
       </c>
       <c r="BS42" s="94" t="str">
-        <f t="shared" si="168"/>
-        <v/>
-      </c>
-      <c r="BT42" s="94" t="str">
-        <f t="shared" ref="BT42" si="169">IF(BT38="","",COUNTIF(BT8:BT37,"&lt;51")/COUNT(BT8:BT37)*100)</f>
-        <v/>
-      </c>
-      <c r="BU42" s="92" t="str">
+        <f t="shared" si="159"/>
+        <v/>
+      </c>
+      <c r="BT42" s="95" t="str">
+        <f t="shared" ref="BT42" si="160">IF(BT38="","",COUNTIF(BT8:BT37,"&lt;51")/COUNT(BT8:BT37)*100)</f>
+        <v/>
+      </c>
+      <c r="BU42" s="83" t="str">
         <f>IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
         <v/>
       </c>
-      <c r="BV42" s="93" t="str">
-        <f t="shared" ref="BV42:BW42" si="170">IF(BV38="","",COUNTIF(BV8:BV37,"&lt;51")/COUNT(BV8:BV37)*100)</f>
-        <v/>
-      </c>
-      <c r="BW42" s="94" t="str">
-        <f t="shared" si="170"/>
-        <v/>
-      </c>
-      <c r="BX42" s="95" t="str">
-        <f t="shared" ref="BX42" si="171">IF(BX38="","",COUNTIF(BX8:BX37,"&lt;51")/COUNT(BX8:BX37)*100)</f>
-        <v/>
-      </c>
-      <c r="BY42" s="83" t="str">
-        <f>IF(BY38="","",COUNTIF(BY8:BY37,"&lt;51")/COUNT(BY8:BY37)*100)</f>
-        <v/>
-      </c>
-      <c r="BZ42" s="84" t="str">
-        <f t="shared" ref="BZ42:CA42" si="172">IF(BZ38="","",COUNTIF(BZ8:BZ37,"&lt;51")/COUNT(BZ8:BZ37)*100)</f>
-        <v/>
-      </c>
-      <c r="CA42" s="85" t="str">
-        <f t="shared" si="172"/>
-        <v/>
-      </c>
-      <c r="CB42" s="86" t="str">
-        <f t="shared" ref="CB42" si="173">IF(CB38="","",COUNTIF(CB8:CB37,"&lt;51")/COUNT(CB8:CB37)*100)</f>
+      <c r="BV42" s="84" t="str">
+        <f t="shared" ref="BV42:BW42" si="161">IF(BV38="","",COUNTIF(BV8:BV37,"&lt;51")/COUNT(BV8:BV37)*100)</f>
+        <v/>
+      </c>
+      <c r="BW42" s="85" t="str">
+        <f t="shared" si="161"/>
+        <v/>
+      </c>
+      <c r="BX42" s="86" t="str">
+        <f t="shared" ref="BX42" si="162">IF(BX38="","",COUNTIF(BX8:BX37,"&lt;51")/COUNT(BX8:BX37)*100)</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:80" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:80" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:84" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="124" t="s">
+    <row r="43" spans="1:76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:76" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:76" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:76" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="124"/>
-      <c r="C50" s="124"/>
-      <c r="D50" s="124"/>
-      <c r="E50" s="124"/>
-      <c r="F50" s="124"/>
+      <c r="B50" s="98"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="98"/>
+      <c r="E50" s="98"/>
+      <c r="F50" s="98"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="124" t="s">
+      <c r="K50" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="L50" s="124"/>
-      <c r="M50" s="124"/>
-      <c r="N50" s="124"/>
-      <c r="O50" s="124"/>
-      <c r="P50" s="124"/>
-      <c r="Q50" s="124"/>
-      <c r="R50" s="124"/>
-      <c r="S50" s="124"/>
-      <c r="T50" s="124"/>
-      <c r="U50" s="124"/>
-      <c r="V50" s="124"/>
+      <c r="L50" s="98"/>
+      <c r="M50" s="98"/>
+      <c r="N50" s="98"/>
+      <c r="O50" s="98"/>
+      <c r="P50" s="98"/>
+      <c r="Q50" s="98"/>
+      <c r="R50" s="98"/>
+      <c r="S50" s="98"/>
+      <c r="T50" s="98"/>
+      <c r="U50" s="98"/>
+      <c r="V50" s="98"/>
       <c r="W50" s="63"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50" s="124" t="s">
+      <c r="AA50" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="AB50" s="124"/>
-      <c r="AC50" s="124"/>
-      <c r="AD50" s="124"/>
-      <c r="AE50" s="124"/>
-      <c r="AF50" s="124"/>
-      <c r="AG50" s="124"/>
-      <c r="AH50" s="124"/>
-      <c r="AI50" s="124"/>
-      <c r="AJ50" s="124"/>
-      <c r="AK50" s="124"/>
-      <c r="AL50" s="124"/>
-      <c r="AQ50" s="124" t="s">
+      <c r="AB50" s="98"/>
+      <c r="AC50" s="98"/>
+      <c r="AD50" s="98"/>
+      <c r="AE50" s="98"/>
+      <c r="AF50" s="98"/>
+      <c r="AG50" s="98"/>
+      <c r="AH50" s="98"/>
+      <c r="AI50" s="98"/>
+      <c r="AJ50" s="98"/>
+      <c r="AK50" s="98"/>
+      <c r="AL50" s="98"/>
+      <c r="AQ50" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="AR50" s="124"/>
-      <c r="AS50" s="124"/>
-      <c r="AT50" s="124"/>
-      <c r="AU50" s="124"/>
-      <c r="AV50" s="124"/>
-      <c r="AW50" s="98"/>
+      <c r="AR50" s="98"/>
+      <c r="AS50" s="98"/>
+      <c r="AT50" s="98"/>
+      <c r="AU50" s="98"/>
+      <c r="AV50" s="98"/>
+      <c r="AW50" s="98" t="s">
+        <v>22</v>
+      </c>
       <c r="AX50" s="98"/>
       <c r="AY50" s="98"/>
       <c r="AZ50" s="98"/>
-      <c r="BA50" s="124" t="s">
+      <c r="BA50" s="98"/>
+      <c r="BB50" s="98"/>
+      <c r="BC50" s="98"/>
+      <c r="BD50" s="98"/>
+      <c r="BE50" s="98"/>
+      <c r="BF50" s="98"/>
+      <c r="BG50" s="98"/>
+      <c r="BH50" s="98"/>
+      <c r="BI50" s="63"/>
+      <c r="BJ50" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="BB50" s="124"/>
-      <c r="BC50" s="124"/>
-      <c r="BD50" s="124"/>
-      <c r="BE50" s="124"/>
-      <c r="BF50" s="124"/>
-      <c r="BG50" s="124"/>
-      <c r="BH50" s="124"/>
-      <c r="BI50" s="124"/>
-      <c r="BJ50" s="124"/>
-      <c r="BK50" s="124"/>
-      <c r="BL50" s="124"/>
-      <c r="BM50" s="63"/>
-      <c r="BN50" s="124" t="s">
-        <v>22</v>
-      </c>
-      <c r="BO50" s="124"/>
-      <c r="BP50" s="124"/>
-      <c r="BQ50" s="124"/>
-      <c r="BR50" s="124"/>
-      <c r="BS50" s="124"/>
-      <c r="BT50" s="124"/>
-      <c r="BU50" s="124"/>
-      <c r="BV50" s="124"/>
-      <c r="BW50" s="124"/>
-      <c r="BX50" s="124"/>
-      <c r="BY50" s="124"/>
+      <c r="BK50" s="98"/>
+      <c r="BL50" s="98"/>
+      <c r="BM50" s="98"/>
+      <c r="BN50" s="98"/>
+      <c r="BO50" s="98"/>
+      <c r="BP50" s="98"/>
+      <c r="BQ50" s="98"/>
+      <c r="BR50" s="98"/>
+      <c r="BS50" s="98"/>
+      <c r="BT50" s="98"/>
+      <c r="BU50" s="98"/>
     </row>
-    <row r="51" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="116" t="s">
+    <row r="51" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="116"/>
-      <c r="C51" s="116"/>
-      <c r="D51" s="116"/>
-      <c r="E51" s="116"/>
-      <c r="F51" s="116"/>
+      <c r="B51" s="97"/>
+      <c r="C51" s="97"/>
+      <c r="D51" s="97"/>
+      <c r="E51" s="97"/>
+      <c r="F51" s="97"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="116" t="s">
+      <c r="K51" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="L51" s="116"/>
-      <c r="M51" s="116"/>
-      <c r="N51" s="116"/>
-      <c r="O51" s="116"/>
-      <c r="P51" s="116"/>
-      <c r="Q51" s="116"/>
-      <c r="R51" s="116"/>
-      <c r="S51" s="116"/>
-      <c r="T51" s="116"/>
-      <c r="U51" s="116"/>
-      <c r="V51" s="116"/>
+      <c r="L51" s="97"/>
+      <c r="M51" s="97"/>
+      <c r="N51" s="97"/>
+      <c r="O51" s="97"/>
+      <c r="P51" s="97"/>
+      <c r="Q51" s="97"/>
+      <c r="R51" s="97"/>
+      <c r="S51" s="97"/>
+      <c r="T51" s="97"/>
+      <c r="U51" s="97"/>
+      <c r="V51" s="97"/>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51" s="116" t="s">
+      <c r="AA51" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="AB51" s="116"/>
-      <c r="AC51" s="116"/>
-      <c r="AD51" s="116"/>
-      <c r="AE51" s="116"/>
-      <c r="AF51" s="116"/>
-      <c r="AG51" s="116"/>
-      <c r="AH51" s="116"/>
-      <c r="AI51" s="116"/>
-      <c r="AJ51" s="116"/>
-      <c r="AK51" s="116"/>
-      <c r="AL51" s="116"/>
+      <c r="AB51" s="97"/>
+      <c r="AC51" s="97"/>
+      <c r="AD51" s="97"/>
+      <c r="AE51" s="97"/>
+      <c r="AF51" s="97"/>
+      <c r="AG51" s="97"/>
+      <c r="AH51" s="97"/>
+      <c r="AI51" s="97"/>
+      <c r="AJ51" s="97"/>
+      <c r="AK51" s="97"/>
+      <c r="AL51" s="97"/>
       <c r="AO51" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AQ51" s="116" t="s">
+      <c r="AQ51" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="AR51" s="116"/>
-      <c r="AS51" s="116"/>
-      <c r="AT51" s="116"/>
-      <c r="AU51" s="116"/>
-      <c r="AV51" s="116"/>
-      <c r="AW51" s="97"/>
+      <c r="AR51" s="97"/>
+      <c r="AS51" s="97"/>
+      <c r="AT51" s="97"/>
+      <c r="AU51" s="97"/>
+      <c r="AV51" s="97"/>
+      <c r="AW51" s="97" t="s">
+        <v>25</v>
+      </c>
       <c r="AX51" s="97"/>
       <c r="AY51" s="97"/>
       <c r="AZ51" s="97"/>
-      <c r="BA51" s="116" t="s">
-        <v>25</v>
-      </c>
-      <c r="BB51" s="116"/>
-      <c r="BC51" s="116"/>
-      <c r="BD51" s="116"/>
-      <c r="BE51" s="116"/>
-      <c r="BF51" s="116"/>
-      <c r="BG51" s="116"/>
-      <c r="BH51" s="116"/>
-      <c r="BI51" s="116"/>
-      <c r="BJ51" s="116"/>
-      <c r="BK51" s="116"/>
-      <c r="BL51" s="116"/>
-      <c r="BM51" s="1"/>
-      <c r="BN51" s="116" t="s">
+      <c r="BA51" s="97"/>
+      <c r="BB51" s="97"/>
+      <c r="BC51" s="97"/>
+      <c r="BD51" s="97"/>
+      <c r="BE51" s="97"/>
+      <c r="BF51" s="97"/>
+      <c r="BG51" s="97"/>
+      <c r="BH51" s="97"/>
+      <c r="BI51" s="1"/>
+      <c r="BJ51" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="BO51" s="116"/>
-      <c r="BP51" s="116"/>
-      <c r="BQ51" s="116"/>
-      <c r="BR51" s="116"/>
-      <c r="BS51" s="116"/>
-      <c r="BT51" s="116"/>
-      <c r="BU51" s="116"/>
-      <c r="BV51" s="116"/>
-      <c r="BW51" s="116"/>
-      <c r="BX51" s="116"/>
-      <c r="BY51" s="116"/>
-      <c r="CA51" s="64" t="s">
+      <c r="BK51" s="97"/>
+      <c r="BL51" s="97"/>
+      <c r="BM51" s="97"/>
+      <c r="BN51" s="97"/>
+      <c r="BO51" s="97"/>
+      <c r="BP51" s="97"/>
+      <c r="BQ51" s="97"/>
+      <c r="BR51" s="97"/>
+      <c r="BS51" s="97"/>
+      <c r="BT51" s="97"/>
+      <c r="BU51" s="97"/>
+      <c r="BW51" s="64" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:84" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:84" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:84" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:84" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:84" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:80" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="1:80" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:80" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="1:80" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AY56" s="63"/>
+      <c r="AZ56" s="63"/>
+      <c r="BA56" s="63"/>
+      <c r="BB56" s="63"/>
       <c r="BC56" s="63"/>
       <c r="BD56" s="63"/>
       <c r="BE56" s="63"/>
@@ -9483,10 +9144,10 @@
       <c r="BH56" s="63"/>
       <c r="BI56" s="63"/>
       <c r="BJ56" s="63"/>
-      <c r="BK56" s="63"/>
-      <c r="BL56" s="63"/>
-      <c r="BM56" s="63"/>
-      <c r="BN56" s="63"/>
+      <c r="BQ56" s="63"/>
+      <c r="BR56" s="63"/>
+      <c r="BS56" s="63"/>
+      <c r="BT56" s="63"/>
       <c r="BU56" s="63"/>
       <c r="BV56" s="63"/>
       <c r="BW56" s="63"/>
@@ -9495,12 +9156,12 @@
       <c r="BZ56" s="63"/>
       <c r="CA56" s="63"/>
       <c r="CB56" s="63"/>
-      <c r="CC56" s="63"/>
-      <c r="CD56" s="63"/>
-      <c r="CE56" s="63"/>
-      <c r="CF56" s="63"/>
     </row>
-    <row r="57" spans="1:84" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:80" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AY57" s="1"/>
+      <c r="AZ57" s="1"/>
+      <c r="BA57" s="1"/>
+      <c r="BB57" s="1"/>
       <c r="BC57" s="1"/>
       <c r="BD57" s="1"/>
       <c r="BE57" s="1"/>
@@ -9509,10 +9170,10 @@
       <c r="BH57" s="1"/>
       <c r="BI57" s="1"/>
       <c r="BJ57" s="1"/>
-      <c r="BK57" s="1"/>
-      <c r="BL57" s="1"/>
-      <c r="BM57" s="1"/>
-      <c r="BN57" s="1"/>
+      <c r="BQ57" s="1"/>
+      <c r="BR57" s="1"/>
+      <c r="BS57" s="1"/>
+      <c r="BT57" s="1"/>
       <c r="BU57" s="1"/>
       <c r="BV57" s="1"/>
       <c r="BW57" s="1"/>
@@ -9521,54 +9182,10 @@
       <c r="BZ57" s="1"/>
       <c r="CA57" s="1"/>
       <c r="CB57" s="1"/>
-      <c r="CC57" s="1"/>
-      <c r="CD57" s="1"/>
-      <c r="CE57" s="1"/>
-      <c r="CF57" s="1"/>
     </row>
-    <row r="58" spans="1:84" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:80" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="BA51:BL51"/>
-    <mergeCell ref="BN50:BY50"/>
-    <mergeCell ref="BN51:BY51"/>
-    <mergeCell ref="AQ2:CB2"/>
-    <mergeCell ref="AQ3:CB3"/>
-    <mergeCell ref="AQ4:CB4"/>
-    <mergeCell ref="AQ5:CB5"/>
-    <mergeCell ref="BQ6:BT6"/>
-    <mergeCell ref="BU6:BX6"/>
-    <mergeCell ref="BY6:CB6"/>
-    <mergeCell ref="BI6:BL6"/>
-    <mergeCell ref="BM6:BP6"/>
-    <mergeCell ref="AQ38:AR38"/>
-    <mergeCell ref="AQ39:AR39"/>
-    <mergeCell ref="AQ40:AR40"/>
-    <mergeCell ref="BA6:BD6"/>
-    <mergeCell ref="BE6:BH6"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="K50:V50"/>
-    <mergeCell ref="AA50:AL50"/>
-    <mergeCell ref="AQ50:AV50"/>
-    <mergeCell ref="AQ41:AR41"/>
-    <mergeCell ref="AQ42:AR42"/>
-    <mergeCell ref="BA50:BL50"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="AQ6:AQ7"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AW6:AZ6"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="AS6:AV6"/>
-    <mergeCell ref="K51:V51"/>
-    <mergeCell ref="AA51:AL51"/>
-    <mergeCell ref="AQ51:AV51"/>
-    <mergeCell ref="AR6:AR7"/>
+  <mergeCells count="52">
     <mergeCell ref="A2:AP2"/>
     <mergeCell ref="A3:AP3"/>
     <mergeCell ref="A4:AP4"/>
@@ -9582,6 +9199,45 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="W6:Z6"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="AS6:AV6"/>
+    <mergeCell ref="K51:V51"/>
+    <mergeCell ref="AA51:AL51"/>
+    <mergeCell ref="AQ51:AV51"/>
+    <mergeCell ref="AR6:AR7"/>
+    <mergeCell ref="BA6:BD6"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="K50:V50"/>
+    <mergeCell ref="AA50:AL50"/>
+    <mergeCell ref="AQ50:AV50"/>
+    <mergeCell ref="AQ41:AR41"/>
+    <mergeCell ref="AQ42:AR42"/>
+    <mergeCell ref="AW50:BH50"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="AQ6:AQ7"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="AW51:BH51"/>
+    <mergeCell ref="BJ50:BU50"/>
+    <mergeCell ref="BJ51:BU51"/>
+    <mergeCell ref="AQ2:BX2"/>
+    <mergeCell ref="AQ3:BX3"/>
+    <mergeCell ref="AQ4:BX4"/>
+    <mergeCell ref="AQ5:BX5"/>
+    <mergeCell ref="BM6:BP6"/>
+    <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="BU6:BX6"/>
+    <mergeCell ref="BE6:BH6"/>
+    <mergeCell ref="BI6:BL6"/>
+    <mergeCell ref="AQ38:AR38"/>
+    <mergeCell ref="AQ39:AR39"/>
+    <mergeCell ref="AQ40:AR40"/>
+    <mergeCell ref="AW6:AZ6"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:AP37">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
@@ -9589,20 +9245,14 @@
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS8:AV37 BA8:BP37">
+  <conditionalFormatting sqref="AS8:BL37">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ8:CB37">
+  <conditionalFormatting sqref="BM8:BX37">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>1</formula>
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AW8:AZ37">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
